--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1098,424 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Constituyente, “paz total” y elecciones: Los temas que se agitarán con la anunciada visita de Petro a Medellín - Yahoo</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNdUJybFRXNlA5VVpKNENsTmpkNGhLb0hkcGk2d0dpZlNLX0JjT29nbHZYTm16dG9ybFFwYjNnMmpMbHRmY2UyaFFWbHJwQ25kb2xKOC1GQ1ZzNlNERV9YZy1CNG5HQ3RYSWZfenhVajdGMkZ1QnVtd0wzSXhiTnlNc2Y2OG16eDRMYmlyNjdBZXR3NUZHc2MzS1FxMXc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Paz Total de Petro enfrenta crisis por aumento de violencia y suspension de dialogos con grupos armados - Emisora Nueva Epoca</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPdTktS2xiQWxEV0wyTlFzX2Y4Q05KRlZMUEtRbWR3VDVZUWNkX2s1QlVIbUo1ZHFhenI1VXVtWVhGZFhzejlhUHJxcWxIeTZuQlFmcnRoNmp5VHdQTXNhUHZsbldqWjhrMktkQXI1SlBuenhwd195Q3c1MzF3aVNPSEFJRzJHZ3FIelBfY3lVZ1BWRHVEOXJRZWZlN0ZmaWEtYk55d1FTbVhGVUFaSExNYzBvYzFLRzFxbHdqeFBPaDZ1Uk1sR2l2T2pJY0l1dFdFRUE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>El papel de la Policía Nacional en el proceso de Paz Total que adelanta el Gobierno nacional - Dialnet</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBwRjBYZmlMZm0zQkJGV1k4V00xSExjR25CSGlUdFVNR2dIRDFWQ3lWaWtFdGdURFpyc2Npbm1wUGZpREFzU1czYkdxQ3VDVnp2UFpVaEZKMk1NNG1FRUNvX3pyV3R3QXk4eVpaNA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Política de “Paz Total”. Intencionalidades y posibilidades - Dialnet</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE91ZHFmOGYya3NqQ3I2aVQ3dWZXNHR1WEFrTndWUEZRNGIyTENucEc5eVBCeHRweWoyRDdwSGk4MUVUajcxenNYV1dQd0JWbHptRGpKV1VWTkVBT0hlbFdGXzI5RmtnRTZXUjlfZg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Los obstáculos para la «paz total» en Colombia - Dialnet</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9xek8zaGlrX0tmRUZmSEFWNGNzbmo5dmZjRlZQZmlWT2JodGFvTS1qaWJGa1R6dlZfdDdyQllwRFRlc1pyUnktTnVwQkl1ejBEcVp1S0V2RWgyaTZwMnpOWGtxRG55TDRrZGlZ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Colombia y la paz total - Dialnet</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE5QMFNTd1E5UzFmTUZ2eHZCbXRuVTJDUVpBeGg4dUhsVnJUUUJFbHNmczFreV9qMW96T1lOUlBSYWxTMUtRTWRtZnJnTHgzNDRNRUhnV3lya2IxRUN1N1V5RGdVb0JsTDFuNHBF?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>El mecanismo de la pena alternativa en el marco de paz total entre las bandas criminales en el municipio de Quibdó y el Gobierno Nacional de Colombia: The alternative punishment mechanism within the framework of total peace between criminal gangs in t - Dialnet</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE80MHFWdXJGTWI3MmU3ams5bVVhZE01YzhvQWo5ME9MODJ3b0NGRDZpVHFaQkE4di01Yk5DWkNqa3l0bm0xMHhtbHRUZTAxWUIwdVpra3BVTU9pWVJWVnJycXlYQkJibE54eGFocw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Filosofía del cambio social, reformas y paz total - Dialnet</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9PR25oalM4N0FmVHB0SzVkSGVZaDBVSUxOZzJCUE05aDk1ekUtM2ZfOVNlUkdUNVFOaS1mYlJoTExTamZxS1RsUnp5U2thQUVDNDBRUk4tNjNPakZrd0hwd2tqb1hjNklKQkNBMQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>El Clan del Golfo: violencia y Paz Total - Dialnet</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE94bDJpZ1pYVkZ1bTUtZzBmOGFXZ0gxTXhfcXRVRkwtaFp4c3Fhd1RRSExHc014Ql9VM3Y2NGZJOTdFV0dONmJOcVFBVjc0UW93aHhtUDFfNTlHWjUteFBLR0FMeDZ1V19kZGVEYQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Cómo hacer gratis un podcast con Gemini y lograr una charla a dos voces - La FM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQZ29EbkN6eWh6QUROUzNJcG5hYURURGROSlRsc3RkWVM2MGRtdGgyTGtwUHJSYjdLbTRzVnJnaW5tYzBVcjluazhBalhWUXF4WURaa0JnVkxaT3VOOXBnUWVTTTRRQy0yMThadktCQ1dMSjRWTUV4Vkw3Q3E3bG1NaXJscTRvRTF0ZnlJT0JBRE9vUndNRUx0TTZBcWdmd3dMd3VnU21YUVbSAagBQVVfeXFMTjRIMWtMczliUlRDaDdwNlhJamdtdnQxMERTcS16Zk1WQnMwUEFFYVZuUGp4ZTF0dmhld2dMbWtXaUNySGhRTXlKUi1ablNkWmFKRlNzUzFrbmVXMkNXN2d5UlNpbXRPclZpb0ZCVU9LWVZSZDlOVkgyQTV6OVVpeS0xcmZ1N1hQMjJfZHR6NEhmVXI5clU0Y2F5dWtWN1Itdk1HN0YwNEVf?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>En el aniversario de los 20 años de “Justicia y Paz”, un nuevo pódcast del ICTJ desentraña las semillas de la guerra en Colombia | International Center for Transitional Justice - International Center for Transitional Justice (ICTJ)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQSFVsYUNXRm1GWkRGQkpiamUxWkJkQmJNa204cFluSHJqU2hwQmMzc3k1bVd4aXpLNWZEZ1BxT2lacmRGbXBBLXBNVzluMlhhRmFoLUt1M3BaV3BiYmRZcjM4VkNrdVYyOHdfTm5Ta0I5SjV0U3ppcXhvMzVWeU02NzZpV3YyV0IzZWR5Z2FiQVI5Z0QtUHItY2hIV0xqUUJ6TVk5bTJNc0JPRGJMcXI3S1dScW1mV0YtbndVQVN5NFNFdGNSQzZ0Vk9WSnIySXdwY2QzLTlTS0habHo0ODZUSTl1RTk?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>¿Se pretenden intereses diferenciados en las devoluciones tributarias?, por Francisco Pantig | PODCAST - gestion.pe</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNcm5aTGdMd19EMUliZlhzTkMwZkdfeFQ1c2EzZkRLdTNSTnMwNThTbWhRTjEyeHpNajdrQUhPMk5YN09lbmFOU3V4ZmNEZTJCMEtMMmpIMXdZeW9hcldjOUFXNW90THJwQjRXSmRiY041ZXVFTkZfQk1MaHpPeVd4UlBRcnNaaGhzZDFPbHRVcUxya1FzcG5oSzBoTno1clcwU0NES0RHczY3RFdHbWsxSXdyOUQyMU03OElWYWNDLU5pS3NtSDJSVmdsbW01RWR2YTBmS0tRQzFwdS1YYTIzOWt3?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>La receta de la paz urbana que está funcionando en Quibdó - La Silla Vacía</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNZUdHM0dWbTU4TGZiMTlrVzV3TWhhcE91X0JSWTNOTFhaT3FZMncxTjNBMm1mQnlwTHUtak5fR0xwMnA2LXQ1bW55UTBDaDV1YXlIcEJQTFZUV05GQ0FuTUo2cTVmWGtXNjFzWEJUZDRib0pMcFZmMDNWby1zSkVqQXRjRDdoNzBhaFE1Y3VnaU9TWGlkMGdfdHowWm1IcjY4Y2cweFNJQTBEdGhHbjZYLWU5Y2JUWGJPMmNFeTBrTVV3dFl2?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Función Pública lideró el primer diálogo social para promover la paz, la vida y la memoria en entidades del país - Función Pública</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOWUdXRW9pMkN1dU1OUVdPckFYdThHR0VYUHZxbkxOUGpaV25XdWxOVGF5VnBrVUpfVWwtenYzTW9wYjMxWHJ0RHFITVNBUThrbG9sV1JyOWJTUzI1M2pGenpmQ0xsN040aTJzVEVWZTlMUk5XdDZsbkJiSVFQTHhxa1pia3lrTmlwR3R4QWYyVFBKdVhwRjFvWEhWT2NvcUdmbWFjd1k4UExwOW5FZk1fWWgwSmo2eUFSTjRKbDZLNEFZclVxNUdJLWFkUjc3WWh2WWc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>«Radio Lecturas para la Paz», un pódcast para conocer la cultura y memoria del Valle del Guamuez - Centro Nacional de Memoria Histórica</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOVVVpSmlNbkE1SVVwdmZzM01fSllGRmNWeXUtQWFrOXJuT1V1b0JFTzRweDZXN2h1cmJ1UFA1dlFjMnpsdkoxQnA5YUc2Wm0zYldzY3ZJODNPWkVRekRWYWN6MWg4Ql9KQmdNbU9DdUl1RG5yNDRhcmFDN1NOdGFDS1U5NzJiSUQydV9OUUxyUzYxQXVDX0RwV0pzbUJwVHcxUU8zU1pqRl9EcjFBV2xOT3pwVTRxbUZyWlh5MVQ5SXAyVlVBVkhpVmNwTFE0Rms?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>El camino de la Paz Total - Global Initiative against Transnational Organized Crime (GI-TOC)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5yNHZfQnhsbHU0b3pXUmFCN0ZiSnV2ZmZvY01kdzE3eXBhQ2FqSXU0TGl2ekFWa05wWnlYX04wZWF4VGJaWjlGYzBYSEhpLWxxMXZaa0Uwdm5XdXFOVXVmVHZYeEM1dzJoQ3doYkU5dlhKTEE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Plebitusa, así inicia pódcast de Santos sobre lo que no se supo del Acuerdo de Paz - El Espectador</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOWXFZYURQdlhnWFlwZFM4T2dza090UjhtZ1hYWkl3QVBnNUlVdXk5bmNVTmkwVXZpVmJQX0xvM2JzLWljUzhaWVhjdlpXUU90TndzV0dnVFVhTkluekM1NVJUc3duODNRX0lheDVoRG1iMnJWc1hieENqYjgwdk10ME9GNHBVWkI5Vi1HWVV1dkpTZmNIdUNyUXFpa2NFbUpudWtHVnBfa3RSUmgtRVNGdnlQaldhT0NDalhCc1hPbkVSUnV1T1BvRU9mSU5CZjdoMjFKUTFfR01fc0Uwbnp3NGdYYlY3aDVseERGZUJUNjBaVkltZXRwUVJENUdmN2dE0gGUAkFVX3lxTE5RWVJPMUdUbWR2Y0JXdWxJR3lvdlJqa2VKN09TQ0VQWE1idzlfdU16T0M1SHZ4VVc4UzlzUXRocHRDOFVxX2FWMHA2UmRpUnlPbnB1ZDhnby04b3hLZXl1WS1PTE9FVXNKTjJGdnFYSGwzN0dZZWFQbko3RU1XZkRjWTVQZ0tVdC1HdllHMGg1a1IzYWFEVkpJM0FyLVN5UXctZGpIbEFZazRHTUVPdDkwRDNweTVDX3hMYm5BZ3hsR0FRVXltVmEycVFMQnZrWmxqNjljeTNCTEZyVFBJRUtNVnhOX3ZsdWs3b19XdTFlU09fUVpJVWxqcVVfd0RKbFlzdDZZd2l5Z095all0NEUtcXBwbg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Quién es "Marlon", el guerrillero al que Petro atribuye el ataque que dejó 20 muertos en Colombia y por el que se ofrecen US$1,4 millones de recompensa - BBC</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE4wdDFlMS03RjVGQlYzVjJ3ZWZ1ZndzLU5UTnNseUlKeHdocXV5NGQ4NzEweFpEVURtNUF5bXR0eGduRzItS3ItNjNTR2VYTWowd0FXVFl5U3BNNl84MklaedIBYEFVX3lxTE4wdDFlMS03RjVGQlYzVjJ3ZWZ1ZndzLU5UTnNseUlKeHdocXV5NGQ4NzEweFpEVURtNUF5bXR0eGduRzItS3ItNjNTR2VYTWowd0FXVFl5U3BNNl84MklaeQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>‘ELN entre fusiles y diálogos’: un pódcast desde las entrañas de la última guerrilla en armas en Colombia - EL PAÍS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQekhCYXhpLWRsTnpwaXhhUklrNURzMlQtbnhvdlB4U3hsbVNfSnJZam11QUtjaWJuTWxhbTZwTHVHWU1yZHFSUm1sOW5yZ1loeTBMRTRCRlRDMnBPMjRsN0pIR0RfM2FOREFUd1JpeTRDbmlDWF9xSXVDRjhiOHRCckVWWEFMR01meHIweUxCeGQxdlY4dU5oUG1IeXdMNV9WeW9pX3otc195RklyekRHa2U2UWJodV81akxCY0lZMXF1anloUkQwOWw1QkxqdHppSTVHQjVWQ2N3Wk5hcTV6T3FLclNWMjVCSUHSAf4BQVVfeXFMUGpBaUppenFNWG45emFEb0xIbGtQQWpOUzhXYmh6QzNpTTZ6V2phNzNGVkNRQUpOeUU3WjZ1OVMwZkJsWkJLOWFpalBaVS04Z0x3eTdXWlhIWjFHd1h1TDNSQ29JS2tfLTJ3a1gxajBlakZDU1cwQVA3MEM1dEtpVXJKcl9nQzBjcy1mSE5vZ2JXVDhRei1MMlZSRXpGai1OeGQ3d0hlN2VRc0VRSVZOYzZUblFMUzAzLTJCakVLd1ZQU3dKSDhIMUlUNEZxUTZSUzdPNl9kTmg4Z00yZ2JtazVDeldtV0pkeDJLVllSaU1uMkg0NjhNYmZ4aXBjRnc?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,6 +1516,116 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-28 23:56</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Choque entre Iván Cepeda y Paloma Valencia por la paz total y la cifra de falsos positivos elevada a 7.837 casos - ELTIEMPO.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxQV1g3WUFMZk00cWMxSWc5b0xmNUJUQ3RaT0dCNFlmVGhTbEF2LXBMTWZDUldVY0lYOUlEd0JWUnVJMW5WZjluU29wMHRPeDlPWWt6ODFkSGRISVlNeXhhQ1ZZRW50ZWFaeXoyeHpKQ083N2lSZEVjWG44OVd0NVJ1UGdoM2xCTWgySzFlWDZ4M3p3dVFWWUFudmY5NEJrM1F0LWZEY2tKNDA0bGczek5TZ29GMFkyWTlOSjJabFZQS3h2S0VNR2VtMnA2dU5iYzJja2RMaVhIZDlRbkNUMnh5LVFJUkw2U3VFdnNuRkh5anBpTUl2VnYzVThIZFNJUjZoTWUtRHVIRWhkZWfSAZACQVVfeXFMTzFmcDEtR0pxV0dxbFJVOFM0UlZBWFA2Ql9zYnRFbWM4UExIN1ptVWVpQ29vdHNtaTkwbl9LblpTVmVUS2JIdUNzdWFqbURIeW5yVzRwV0VKLXlqS3gxVC1vSDhBakMzRXNKUTByOU5VODFBMlFiZ01INHJrclpVdk5JRC1HMGV2eVo2d1FCQ2dyOU1JRmhUSmItdHNzNUZLT2ljQ2pPOHBMc0xVSzhUc2wxUWRoWmM5VzVWamlwUUhjaHV5TFB3b1BJMTVQRS1LX09ISzktRFhJcnlKdGhZSFVUSlcycUhKRF9jc1dpLWRrT3VBRTNMMzBoWkM4dFltaEQxUTliTTZhMnNkT0psX18?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-28 23:56</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Constituyente, “paz total” y elecciones: Los temas que se agitarán con la anunciada visita de Petro a Medellín | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOU3FweWtDWG53aTdEMUI5RnlaTnJIYlBhbW9USm0teHgyRllYZTBVVXkyajZwenZqSWhvX0laVzNjcHA4ZHgxUzNUeGE5QWVPaU9vY09vbEFpWENFZnBqbjFtWWlnV0lMR3R0aV9tUW5zNHM1a011NWdBLXZSYjdGU19FaWlRam9TcEhTblowZExKc1lVRjYzdlBOMHVJbkVPX1ozQXVua21fRVYz0gGyAUFVX3lxTE5lX1ZoaVd6SUJMMTM4U0RVLS1KY1JpY2M4SWdCYVdDTjJMUnNpdlZNUEZoSkRxZ0RLSkJHdWd5ak9ENVdZcURCdXUxLVgySEpveGVWQWxxRXlCam9RSV81R2dwdTl0NFZvZTB6bi1mZzRKLW9teWlVbWozZjVFZjRnek9GclN5UUhyZ1R5ZkdEZ1BuX2JLR0RTSk5HOU5FTzJDelVKVXlrYjk0SmhsVmcxV2c?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-28 23:56</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Enumeran en vivo los errores que se cometieron en la paz total y que desataron ola de violencia: “Petro lo sabe” - Revista Semana</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNNUw3WHhkdFZKeEE5Sk9fZ01KcUc5S0RSNmc1eDBfUldjMkRTbVdSRTYtcWZPMmlEU0V0SGU4MDJzX05IcFdCNHAwNy1XVEc4dWFqaDRma0JmdGYzcW1HS2xQc3F3blZTWWV0cFo1VFRIU3pFT25BZHh2RjRLcEI1MWZHZTd5RWpUYUtMRzdsaUpleTZtN1pYeUxsRzJnQWRGdUt1ZGhKcDFNRmJKZmdPWW8zcVVsQzExcXVXRmVOdmVKaDNVbVZSakNheU1wako4eFFUUXlNQ0lGNkpGdU80WE1vekdYcC0tNlJiU3E4b2hOY01LUy1DRFFhdk1wVkhBcjFTZGtOONIBjAJBVV95cUxNdW5taXJYWlhJUUlxUDhvY2VacUdlalhDVjJDeGwtMWhiWkoySTlVOGRGdTZJUkV0SWxQNTY3N0dIWkhoOFlMVzVmakk5cnJwNDJUUTN1UDdVejMtQm1jOWFXczZUT1FhRUNuQzlteDYwdnFkV19ZY3hteTBJaVR6X0JMYU5rZnlmTTh0T2E0bWc2bmNrWm0wdFJWZEQ2dDdzUTN1RHNKWmZxcS1DS2RPMXItV3hacUE0UmlhMGlQbXBFV0xhOHhSNXRZT2oxc0pvdHo2d0VnX0lCdlVaVV90SWlUeDFvdmNXMVJ3a1VHTFQ2WU43cWFaOEhKQkNaUVRVMm9yajR1Q0pnb3do?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-28 23:56</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Revelaciones del bajo mundo - Cayeron “Álex Mentiras” y “Jonás”, sobrino y socio de vocero de paz de bandas - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOcTBYS0pGOFVHZDVMUEQyOUt0Mm5ralZFTkhpRGVBLTlIaWlaeERPUmw4Y2NKNHQ5TV9ZRWZuR0pyLTN6c0dJTmhQMk1mNzRnQUhoSHJRYXJzRzlacS16UEUyeUQ4T1JqTDY4NTRiMnNHYVpncVBZWHJPTWppcFU0bjUwY0F1VU5pZ0ViWlhodC1BS1BfM1p3azZDM243ZWYzZnc4N1pkaGxvbjB1ZmRtMXFfaE1kdF8zTkZvQnRkaTF0MkhpWWl6RWRxaWVVOVRVTlAyZg?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-28 23:56</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Corcho vs. Cepeda vs. Quintero. Listo el tarjetón del Pacto - UNIMINUTO Radio</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOQU1QeFRCRmlBaWUtSHU3bF9OOGhDTDkzWUtYRFVCYkNMS3lmNURoTTJ2dDdOc2hsMHhVWTA3SzdRLTdCZ3gzZ1owUDM0YXczWGNZZ0hYTkFoV25sNEdqR0ZZSElVak1ob0JBeFdoSWN5YmV3Rm1heldEb0N0QUxLQ0lvR2NNbUg5VEtOOGEzaU9RN0pVMEE?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1626,6 +1626,138 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:19</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>El fracaso de la paz total de Petro que entrega nuevamente un país incendiado - Las2orillas</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPYVRTOXBxWVZvSFRDSk5hWmdkRkZYWEdZdDMzcjFZQXhKZWNibDVKYnVMMlFDMTg0cWVVbm9uNXVlQ3prSGhpZW1rM25qVWNjUHRXM0xtWkd4Rmd2MVFHY0FlUk9pTkpJQ1dBbFJtVFlWYXBFMklEaTVIMHBSTkZTUE41cjdXZndkWGV6Ym1Jdnp0MjFwQ1FzVlhDR09RSF9jb3dobTRGZi0?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:19</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>“La sangre que hoy se derrama es consecuencia de la tal paz total de pacotilla de Petro”: De la Espriella tras ataques terroristas - ELHERALDO.CO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxPbDZLNFotT0RpMUVvVjB2eXFGdVp6WFc2UUdEZzNPVnh6UGVaLU9FSTA0N0sxODRXZzNIUno1WnFVRTJlenZpa09BZUZWOEo4TDFGczFuNnQyX0tRdTVRQU9tRV9FVDQ4YnpEdWtKMC1tUVdreFdOQkVkaG5nT3NnZ2V4dmpUQnlYcVVSYUgxM2JCbHVScVV5aDJYVVQ1UFAtcmItMHliOWpVYUx5eE1HTDhUcXVkQjlTU1RzUk5QMHpUbmc5dG1Fc3pPVVZRSzZVMzFPMFRka3VRZU5CRDJYWUdheWxPZUFSSHQ2QlE4SXNIU2FjTWhzc3ZIS1JJcHZyUy1B0gGeAkFVX3lxTE5PbG9PVUZIRlA1U1lEbTI2T1hvazBSc3VERGtkejd6RFNLMVBLaFJGWXlBVEh4cjNLTWNwMjIzV0s0LVNTbWJ1TS1nZzVidk5lSnU2al9pSnNqTHB2c0xJVE0zWWZmV3R5YnYxWFdZbFZOWU5XUTFxb09oVmVya1gtVGJTaGJVMHVWb0tpdnQtcW0zaHBiRkVValNrekZMeHJ6bHh2OUNsZzktNnBsSFZjblNwRXM2cmxDVklDb1NZSDhDZGlBZlY3ekF6WTV5T2JzcE9rVnF3TThJeE1uLUN2NUtUWEYwcHAzQ0hnMXY1b2Q0QzdpRzhOWEFfblIyVnlIQkpIdUFlSV80S09uTjdPUVV6TnR6cnh1OEF4YWc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:19</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Duro informe de Asocapitales sobre la 'paz total' del gobierno Petro: 'No se está logrando contener ni reducir la violencia' - ELTIEMPO.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxOVHdyUTZsa2VadWp3ZU9pMDItRm1QWkl4NUduLUtfOHNVY0R1bVVHMnp2ZHhPQjFiVEJYclFaamVYVzd5cy0zcGlHYWdnenM2UExqclp3di1QbEs1RHlYS2lzVUZjZ0NaWFpDM3ZUczRPUmM3Njd0TnlieXZSX3dhN3lvRWV2TUhCR29DMUhNMnRRUFJxbUYxbGU1NnNNQVFyMExMNzBkZGNBZmF2UlozZDlCd3hFVDRQTFM2eFZLR3BhQkE1eXg5WHlhY2V3SDcxZlo2OWVwUVZfbl8tNkdRLUVWVVJYei1kYllEZ0pqa1g1ajYzZUptMGc4ZmNCRmtOcTluT0g4MW80VVRSaUVEU3JGbG8?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:19</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Quién es "Marlon", el guerrillero al que Petro atribuye el ataque que dejó 20 muertos en Colombia y por el que se ofrecen US$1,4 millones de recompensa - BBC</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBQME9WVUJDX2hGdk01eV9oU0hkWW1jZXZnZ2k1Q1FQSFJOcnpoRU15c0V2cGtNMXAtQ3VaY3BZUS1wa0Q0dTJDSnJHa1UxdEFuMTYwUFBEMnU4eE3SAWBBVV95cUxOMHQxZTEtN0Y1RkJWM1Yyd2VmdWZ3cy1OVE5zbHlJSnh3aHF1eTRkODcxMHhaRFVEbTVBeW10dHhnbkcyLUtyLTYzU0dlWE1qMHdBV1RZeVNwTTZfODJJWnk?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:19</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Llega dos de cada diez: el pódcast que cuenta las historias de las víctimas del conflicto armado en Colombia - Unidad para las Víctimas</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQY3lmOXRrVkZVTXNfbVJ1VERjRHA0ZlNkZ3c2TkhtTFh4LUI4bmxVc0Q3ZzduSXJReGNYdWtnQ2tNdEZMaWVzcmhOS1hZWUY3LWhYdjFVMmdmbmhuX21PNXgzYjVrbTZTU0RHRDI3cGdQYzZ1Qk1KYlMtVXNpbDlMZHZ6YmJQNFJkMG9BY1Rwcy1XVFd0ZU83S0Q0REFQZlFDNnpYaUZFUThEMWxrTGlIcnFOeGEwYnc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:19</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Summary for Policymakers</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W4300009529</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1758,6 +1758,50 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-29 23:56</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Asocapitales alertó por resultados de la Paz Total en las principales ciudades del país: reveló preocupante deterioro en la seguridad - Infobae</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQaUVyeU1VNGxBbTlfNFZsVGNjdWFybzBmQmN3U2FWaU9Vb0c3LUI0TE5MYmQtNUo0UGJBUUxONHhLbzFkbGtva2hlMWFKd1RFU3E3a2NqNy1HUkZDeExRaTJGTWU2eVdmRVJaSmo2eXVibFFYZkU0SHpjNlM3Y2lSUVY3Mk9TM001SWVEVklPbWR5MDVtN3lnVi1IQ3AtUTVBcUZsVkFwZnlEWlpwNy10aEtESEVyU3dDYm1saWtjcXhBaURPblFHMWFLd1YzMV9NaFVjSU5WNG9MbDBwQlpma1NnUDZBbXhhZ0MtX2VybzQxeG0zYmx3dVNLRkJ6XzNNaGNqRHdNbFnSAaMCQVVfeXFMTk5UTkdJMnFGZUVTaGYzOVlfb09aTFFwdVl2R0c3MlJIZ3NPd0k5czFyR1ZwVmNqWVRVcDdjTWNDaUNBbTlqZlFpcE1Jay01S2FzLURMV2RMeFhORXpWeUd5VUFYUGtNTW5YM0Z3eWtWZmVIR2loNU5NRXl1YWNNd1A0Q3lMNHcwNU5ndENaa3dwTnhjajJiMUcyUUdnb3ozWkEwWVFiU1hWcGZCVEZvd3VmRGRUSGhJT09WUTBsVTdmbjZQQWFWbGpXRENxcHVmYmJkZ2FBVXlCSHp0YWhlbm02U2J2anFUZHFoa29IeTZjMDAyalRRM2czYXJpRFhMajVfVkxFTlc3a29jdUdtekNQaGdUMWIxTU5lSWpMX2xpTU9R?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-29 23:56</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>“Que respondan por el fracaso de la paz total”: Coronel retirado al gobierno colombiano ante oleada de atentados al suroccidente del país - NTN24</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNUmVLVUFHYnVWdEV6UkpIZmYxRlVESm1pLVg4bmpEOVRsVUZOejY3SlpqRTdSNFNhX3lSRDZIRXNwbkd4R3NvcEh0cXBYLUdBdExMcU9PZVdqU2NVWW13SnpDUXNqMzRWdWNfMk9ETU9NRXdNdzBUcXdDU2F6cVN1UXJwSGtYNWZNWmRLR2VzZ2FWcGQtTi1kOUYtNlZHeVl6bERMcTIxdWh1U0VySmFQaFNPOTI2VWs2UzBUbFJodlZ2OWM5cEpqOXBocVRvNkdjbzNUSW1oTTlGODRvdS1XX0h1VVNlMmFYTDREWkZydUNXMEVUTlJFaGFCbmY5Mm9Ea2UwVGR6d3BPVlp5MkhVd9IBkAJBVV95cUxQM3lTcS1JX1dGWHFkNk5EcmdaODFmYVE4dHdnQXRqZlFOQm1VOTZlUm45WGFHN1BUUHdkcTI5NEp4QTllNnFJQ2FrRHZEOWJfRzhBZE14VG43T1o5NlY1T21BcGhfYmVRY3h6VzdaTE5IS1BCRHk3SnNlRE9mYW1FcURXcEFNOGVOb3dzaU1td0lJOU5FZzRTOXNlclhfeWdoM1NiTnBWRGl6blJ0emJjeGNvTjR5eFl6NUNlZkFxODNILUdHbmUtUEFkZldHcTlLSDk2VDBhMkw1eXZhZWFNVkF1b19fbF92akZWTW1uVUZIdjRPOGpsdVo3dk5WdXdmcFJKVVVhSXowRFlhR0xLRQ?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1802,6 +1802,72 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Asocapitales advierte que no hay “resultados consistentes” con la paz total: “No está garantizando seguridad” - ELHERALDO.CO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQS1dOcXVHYUZHVUFjN1p2eHdkRzBZNC1XSWN1NDVrLVFMOGhjOUdhdEgxNF9ZcGRuZUtKREoyZDJiRGpuZEtsdUVEejEyOTNDS1M3Ny1DdVY2VkQzVUpkVms3akFJcXRIdEl4a0RTb2VVcnI3WVBjLTQ4QzFOS1ZKaS1Nbk5rTWxoem5wekR1em53MEt5aHBvSjAxUjNlVFl1VldLNUNoUTRQaWIyT01JRlYteTJEX3hEX0RHLVk3b0hJVU9XeG9kbnJPOHE4U2dLNENkQnpwQ1lzRWlielZ4Qk8wYVXSAf8BQVVfeXFMTkdoN21tVWxSVG56ODNLclhqN0Y2SVpQZjFiMXpJT2lPZHRkd1N0OXhWeVRzRHFNMjZiZEg2UUNmUExyQ2tDM280ajJ0NEFnR2tRSC11VzV4My1aWU1VWW1KY3k2T3hrWUtjeXhTZHRhaDBGY3hiWGp2Nm9ZUmZHRTdjaVFMZ2t1Mjlra1M2RkFKdkhieVJPLXFYb0ZRLXV2Y0RxbFp3Q2s5Qk0wU1dEYThmQ25Fc0VPbmo1TWprRlY3WTRxZmt4ZkdEckVDdGVzSG5LUzZFWkFIOVJQZGp4LVYxU3h2M0oxNmhMSENKVTVoVDRkRDVtbzhVZE40UkVn?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>“La Paz Total entregó beneficios jurídicos sin exigir medidas reales de seguridad”: Asocapitales - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPaDNXdm9iQWxxWXBaNDZMUldKdHhUa285Zk9PYU9mak55dG5EdWdxNXhzR2JvX293MjV6cFEzRjhrWW1ybWVXdUQyYnhGV3lJeTJGQUxlazJ5b20xVXMxckNOZnhkVks3VHVQYTB4SWVubGc4R242Qktld0FqeTdtUEZYR2Fod2NveWZ1WU9YMjBIWENTRHYtRy16b0hURFdrcGxwajdVR0VJWVE1bHdCalB6UkduU2lYdGR3?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:13</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Calarcá y el DNI: las claves del último escándalo del gobierno - UNIMINUTO Radio</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNVHFmRm45dW14Y014NzF4X3FoMjRuT2cyelRQblQ0Vm95Q3BiWGotOXJsYm94Uzk1Q19hUkpxcm9XZUQwZ1E1eDBlTXp0WHh6ZWtfTDdjeW9YazdWbTJDa2tEUXk5M1pBSEZ0b2NMV0o4SXVLU2JIZmpNUjA1c3ZhSmY2dUZfR1ZXdUVvamJMUkNaYVhGSnZabmZOLVc?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1868,6 +1868,116 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-30 23:54</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>El candidato presidencial del Pacto Histórico defendió la ‘Paz Total’, al considerar que la política gubernamental no ha influido en la expansión de los grupos armados en el país - facebook.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOTVZ6ZjYwRWJ2M2pTLUFnWXp1MEc0eW9aN3AyNzNJOWtTcUh3Ynl4eFV0eEhUWkp2RklaS0VNYk5mbXQ3b2RISlJhcUpJa0Nxak1uaTRWQ3VHTUVwci11LXlGVExKZFlZc01YclZVMFBvOFo4UTBFVUdNTUVDS3NUbHRlMTZXZVhmRWdoNHUtVWNJNm1jdWt4Sjk5NnJMREJLaDJGbEJlN0JYQjBoeFFRMjFRTl96SFJ0cml0a0UzTm1hVUloUGhwazFwQ1ZMSU1HUm9oaXpUU3Job1lMZV9CWWVINzdSbmlIbjlB?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-30 23:54</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Lo que le espera a ‘Calarcá’ tras la imputación anunciada por la Fiscalía: su salida de la ‘Paz Total’ depende de Petro - Infobae</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOSVBvNFREaG9FYWNQcjRhTFJ3RW50OHFrcVJPWHp6Q1g1X3FYZ1N4bW1mNGNfZDBDZnNEWDVjenNJbmlKQ09ORWxhekVxbHM4bmlTUHVPLWhEVWp4TWtIcThnNVlrc3RtNk5iWWhwTTR3c2VXdXBIS1JyTmZySUQ3cE5LVGFfOG1lV0tseXo5Q1ZGdkVTYnFUTVFDazI2MTVYN3dOTWNkTGpGSTQ1Ym5VMGkyVUdGUTNJZGl1VE4tNjJvYUMydl9QRFUzU1c2Z1RCUWhsQS1hWmZtZVVfRFNOVWlzdmcxNXlxM0hLUjQxTUvSAYsCQVVfeXFMTmR0ZE4yVXFFbEgyQ19XNU1TQTQtbjNCN2d1WmlqUE51emd6aEdoVjFPemlZZENxOGp1amVBcFhFamxscU1EVnZFZ2c0cl9zYm55akV1bmkzck9WeWd6RUpXbWFFNkZoUW1vTDZ5dUZta1FrRjFLaUt5NFpNYUFLVjJNU3RJZHZjU2c1UURqaG4xWmIxNXdsWklQYUNicVp1bFNIT1hnakVMa1VCOWFkWGVNeEVTME9JSjUtTmhGTVZtMEtqcThrZ2N4cjlEaE9VUll4TVY0bmU5UTZPU0c4blZFYUd6MHdlTFhBdHNlOVFlOGFJMXlncUEwcm12ZjdFamFIRUZtbVV6Sk9j?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-30 23:54</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Los atentados en Cauca revelan los límites de la paz total - La Silla Vacía</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQbFFFU0J1ekxrTWpxQ3o2dHpBUUlUUzdvUDZMR2J3a3BFa2hrVDZkRElIMVRkWk9XR0JwMG9pRXlVQ3hlY2RNLVhQa1RoRjFRbkFuVEJGaFZKa1lMRzJCenQ2SEFiOEh0bmV1NXVIOWI2al95Z3B1SVI4eUtiRlpseTlYUnByeGlOd0QyWXZrRnVkX1FsQzR0bHQ3UkE5cnBwQTJDWlMxWVU5QXpFZlg0Yk53cEhIdVljN3c?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-30 23:54</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>“La Paz Total entregó beneficios jurídicos sin exigir medidas reales de seguridad”: Asocapitales | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPaDNXdm9iQWxxWXBaNDZMUldKdHhUa285Zk9PYU9mak55dG5EdWdxNXhzR2JvX293MjV6cFEzRjhrWW1ybWVXdUQyYnhGV3lJeTJGQUxlazJ5b20xVXMxckNOZnhkVks3VHVQYTB4SWVubGc4R242Qktld0FqeTdtUEZYR2Fod2NveWZ1WU9YMjBIWENTRHYtRy16b0hURFdrcGxwajdVR0VJWVE1bHdCalB6UkduU2lYdGR30gHAAUFVX3lxTFBvLWdkV1R3TDA0Q3NuUU1fVms2Y0c5SzgzM0tUX2kwZkE1TU1ENTB3TnRyU2ROSlVzcnBZeFdvU210emMxNlYxMFFPc1dFdGdVU2dNNWViWVRXTE1tQ2dBVkpmOXBobXBuQzhhWU5rSU44bG9wWV9MV2dpYVItUDhRZ2x1U3FzeW9tODRkQVpYN1BQRUtmeWF4UWpFbDlDLXBJV0kydTJsRE4tdDR4UHczcDNJWHBGVElYaTBOVHJfVA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-30 23:54</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Iván Cepeda habló de paz total, debates y constituyente: ¿qué dijo del gobierno de Petro? - Noticias Caracol</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNR3V3anFMQVktXzNpOFhrU1lTZ0o2MEptV1RtdXVmTFZKd3F4dFpUS0ZYYjNrbFN5V1RHSk42bWZUZy0wLTVkN25FT21RNGF1eFVZQTNPcU9id2drXzZxY09ubWdIRm90U05FXzF6aGxLcUpSOEFqQ3dhdWZWZDRtdXd0OFBJQmxIN2d2bG5PMy1fay1vRVEzVDNUelJmSWhnWjZoUHRkSXc3WjF0Wk54SktRWmo1R0dZSEQwVkxrMm1IbnBkcEVkU3UwaFlkR3BRSkN0MkNMc0pFNnVBUFBoUjlFQXBHazlVM2pZWGhmaXZuVlg5VXhF0gGEAkFVX3lxTFAxR2xXZWZ1RHVOU2ZSMWdrcTNpeUs1NmVrWjRaa21sVGtkNFpJLS1aTFRnbnRmM0lfNk5TRTNyWXNPSWFuM2hVMW9vNjdndkxKRTMxNVltaDFEUUF1M1VDWVd3NUVPNGFpVHh4alg0ZHMxQ20zb3dIVjJPUXlVRmNMb2t5RFl4V1VsRkhmLTVNWG53Ml96NU1mdVlEa0NiX01PM21wVWZvYThEQ0tkYnJ5TldfQjZSaE1nMUJvdHV2NTZ2c2M4d0xZOUJTQ0pDZEw3TmpyRDkzWHcyVnJHcjVNcnZRLVdNRWcxaGRiMm40SWdkRXRzNm1ucWtJbWtVYXpQTThM?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1978,6 +1978,50 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-01 13:43</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Violencia en Colombia en víspera de elecciones como muestra del fracaso de la ‘paz total’ - PanAm Post</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZDlMS29BbjFJUnZwaUFkb0hfR2VQbzVDVG9XdWVfYUZrU241dDFuenpTM3dDTjRNMFl5UG5tUWNRYmFoSE5xYjB2VG9zYl8wT1pTN0RmRXFlOXpub1NlSkpwRjhWR0pidlhEd2dTR2JGcGYxSkVtaTFIb3poUjNOSnk3Rm1sQUlXajdjZjM5NzhLbDhWMFJSQVJxTEJwZm9zVFk4bFJvUkw1Z09OU1ZJT0RVenZ5cjRVbVd6TlhTd25leUpQN0ZQLXVmdWprcEYxeWh3VlpZMDRZcG5j?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-01 13:43</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>El candidato presidencial del Pacto Histórico defendió la ‘Paz Total’, al considerar que la política gubernamental no ha influido en la expansión de los grupos armados en el país - Facebook</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPUVlDTjFRSFIxbERfSWlvR3NwWWp5ZnVfWkcwVmY4UWJwN1ZHRE5hZEt4bzk2dG1IeXdBd3pydFN0LVZDd1U4cjlCZTY1c2pXR1h6cURfSGFQU2RQWS1UQ2ZNQWpna2ExdWVEYmpFQlp6d2hBMGZRWGFOUThlVkk0ZDZXWTRneEsyLU90TkxySk5sZ2UtYlhkRUxNNjNDY0tVWUVTdWFUT2FIMGNZNTVjWVBwRXoxcHp5eHM3dFVRRkFYODBEZ3RIMlNyTzZVV3dvNG9FSTEzRGJ5eVIwWjd5d0VaaXpkNTJkc2Jj?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2022,6 +2022,28 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-01 23:53</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Paz total en el fútbol europeo: Madrid, Uefa y Efc pactan el nuevo orden - MUNDIARIO</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQYk5jU2xzQjF6aHl1bVloUnV2Z2FHTE85aVcteTZOWlNlZk1NblhURGlqMFFIc2kwZmtuNHF5Q2RZb3BKaXlZUGYxZHFRbzBFQVA2R2ItRDVzMjQ3d3l1Z010SHNRaXh3YUlsWHRzS3A3d0xneWJJcjRsWnVNSzFjT1FUdGl5cVVfY3dNTTNsZ3AtTDJRM0Z1cnpXREdnY0JwYmNiZEJBcmltTW51QUtMSGtabkdFd9IBuwFBVV95cUxQRjB0dXg3YzZnX1JuUmFNLUR0ZDNMN0dUc3ktdG1mTkxVSDFYU3VGS3JQMEdLejMxVnhXTDFyY2pvZDBQYXJSUVVIclNSV29LckVJdWtjczJsc01hM0llSlZmandRd1VhRXlGSnFzR2Vwel9WbDNaRDVKLVhKd2JZUkhRVzhENHlfUTRsS09SUk95SWo1ZGNWRFJBMDE2bXF4N3VGVThRZURtQ1UzUkI3VnRxd2hNaXgxcklR?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2044,6 +2044,72 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-02 13:26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>El laberinto de la "Paz Total” - laopinion.co</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9JcWFWZzVBMnZHNk1LWGlrZU0xSERod3lLNHRYWENlcFUwTWJpLXpXVEo2TTFhV0tjdFpJd3dwYU9hQ09yemF6UnBWbnUzVUQ0dnNCVk5SQlNoVFBySzhTYWNLMXU0NDY3UlFUTFgzU0tMcFU?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-02 13:26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Los dos primeros años de gobierno Petro en Colombia - Latinoamérica 21</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOaHlPaG16UmgtQWhON1lNcFowdVNnTE1DQlktVFNqRUUxNkZ5RVFZQ3AyTGdSak5JbWxuUDdmRGFPLVlnYVFPNzI2SUdlMWswS2cyeW5IVHUxdjdMTzFWMW93VlFxLVRFVGdUYUN6YXJldngtS1dQYnVmcDl0RjU4Tmd5UmkwSG93NWU1anVmREFKNUp4S2c?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-02 13:26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Conversaciones sobre paz: los aportes del feminismo y las formas de participación - Publimetro Colombia</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdnRLdGVRRzhQXzA5QUlOTFZOQjB2QTRWS25NakVkZGJ5VEVpTmRsQlcxZldZNXdQaWRzeUxzQm43QTdQbWp5c2RqcDZEaHRPazlhbXZxWjh5b1ZkYWhSVkFZZFBPR3M0YmNCeGgxcmEzd3hUa1FlN0k0UDFSbFM5WEU5NVdoc19UWW5iU3lfXzVudXFGSHVYVEpHOXZYdFV0X1NPM2FIRWlQUWNPX3pXcF9hU3FtVGd3YTFpbXkzbEhuQWppVHc?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2110,6 +2110,72 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-02 23:46</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Golpe a la “paz total” de Petro - Vanguardia</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxORkJOYXdjc05xSzk5YnFFdHdMNVJvSmsza0hURkpEemxBUG5fcmNrQ0VoUVVUU0V4MnVuNHNBdFJ6NGg4Mi1jMVlkaVNtaGI1dVlfMXQxUGVWUDNreGtLV0VnY3VzRDZZUEVFYlR3amVCQmdMMUkxZXptMklVb3R0b01Ydw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-02 23:46</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>“Conmigo la ‘paz total’ se acaba el 7 de agosto”: Fajardo - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQVklrUDZFZHl5NWQ1a05qUUVkRHpnMzNzTHkxOG1RZzg3aTNoV2Y1Qm5qOHZfY0RwZlNVcEptNzNkYU9leEFVTURaMDZDU2lwc2FuODhNa2xtRW5hTXl5dG9zZFhKMHI3R1dMQnRSX3JzdTVVWGtERzhqR0ZmSkp1R1l6cU1fcl9yZTJzVXppMEJMbmZVRlZLZEkzYlFWOC0wS1R4MGNtQ0NjOFNlcmhv?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-02 23:46</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Los podcasts más bacanos de Spotify Colombia para escuchar este día - Infobae</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOMmNVMHc4M3B5RzdGRW1kNW56aWRTVEQ0b1c4OUh0aTlsVzU4S0h1elA1WHI3b2hsbUJiYjY2Y0lqSUQzXzFzX3Q1NGc2NU5lQTlTNVJyLUhURC1jLUhOV0J1RDBGbHpYSHZQT3VJSlByRW84eVJnenVPOEpjUXMweC1KNmU1RGVsQVlWZDF0VXZDeGJkR1BXTHc0Y1l4bVIzZVpyMl9FcjQ1SFRq0gHHAUFVX3lxTE5GLUxXYkhaamtBSWt6bnVlb2FlVnFjT3l3ZDE1bVg2Nl9teHhfbHZsVGZFZXZUeVZKT1BqWk1CRXZJX09rRjVjRnhLWDVuMTdHRGNkaEJtcGJ6UkRUdGVrSW9JSHBtTFQyb2tPU2pjN214TVJxOU1IZDJWMUtUaF9BcUJ1a1VTdGsyTGtkXzVOWkg0S0ZMUUxVTE0xU1k3dG1TSHlnaVJlXzlaV2dUc0kxQUtyOEZwQ1J3M3dsV09pdllIeHZpY3c?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2176,6 +2176,50 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>El desayuno señala cómo va a ser el almuerzo - El Espectador</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPR29qWGU1TEdDRm9TY2lvZk9fOC16WTdOMHd6QWZldlVsTUkwYmc3S2NRWGRKVXBVckJUZFJLNzR6UXpBZjBVSXVqUkJCeGNQZGpQMmhHT3VnNGN5cVBLcDUzUUd3cU9OajZxNDMyRE52ekxrclFtbk01Q09wTDRSdUxPOEc2bWN6UG9lUmtFUFpja3lUV1M3UUpHVEZNR25YbDVBTzdTU0REZkwzM1JBYl9Cb3RaS0hGS0HSAc4BQVVfeXFMTW11OHlyX0Uxd01rSXBNUUxwelpNWnRFY3NEOF9tR0F5eTRPMFJ2UkFaRy1XWmpPLVFKUGhkSENxbkdTTHpxOHpyVW80SGJBZ19YQnZ6dENyR0ozNWZRcE54dFdSTVhqaWRWTWpsZ2YtbWRMRGh0dEJ1d3lVdDFXd25aMjFZSUdvYnlmekV1ZEdYWUo5TXpZRnp3eGJtVDNja1FacWt6NmpGWmlyb21DTTA1ZlBvczJGV2s1cm51bVUxblRoZ1kwaXl3ZWtUYkE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>“Conmigo, la ‘paz total’ se acaba el 7 de agosto”: Sergio Fajardo - Yahoo</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1YZVlMSEdJTEVjT3IwY0diX3NlYkppOUI5cHlQd1VSd09hLVk1djltVURIdGEweklZUFU5X0p3QnpQMTM4RVVTSlZic3B1Y0R0MWlPNzFlOXpia2xqUXphcVJKdVhmQ0tZWUtoXzBoc0cyVTkwN2Mzd2dCcmdrVjg?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2220,6 +2220,50 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-03 23:50</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>"Pondremos punto final a la paz total": Juan Daniel Oviedo desde Cúcuta - La FM</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQblotVFlYS2gxelhzbWswbnlHMllZRXR4Yno0OUltelNiampqNk50YjNpM0JVVzNVLUJfSkJWbmpGQ2pMMXdHYTFfUUNJa1NSZ0FBNmpYSkFhbGFlajFfd21EZTg3b2I0cHpYX1BBMmQwbUFGRmlHRnBNYTZkRDFNblhJRGkwRHZFOE51cWt6SWpwM19kRHo1Q2QzTEROQ21TaTN1SWwwUHROR1pxbVBLRVhOV2JyWWFvcEpR0gG7AUFVX3lxTE9fQV9WWGtVODNQMjI2b1NEdXR6TDhjaEFxeEY1ckt4Qk5BR3VsWWJfMFF0eEdtU1RHNEtIX3M1d1JyV0hBRFpRMVBuUWxUV09fUDYzZ3gyRW11YVlqMXZmVC03cWpwRlkwLWE1dzNoamttVGhSaGNHMTY1dWFUYUM4LW5hNF9YYnd2WmNUOEptUjNLUjdvMDNkVjBVWFdDLW9yVzBHc29ZWUdzWlQ0TWktTE9QZm8yaXNnWlk?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-03 23:50</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>“Conmigo, la ‘paz total’ se acaba el 7 de agosto”: Sergio Fajardo | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZDZleUJVQUxpMEFGcmhUTzZ0WGtiUVAySmhvS0xIdjJ3cVFvUlFHNEtUMkFPRkIxQjhydkJoZDlwdXFWbkwwQlNvZ25vTzZ4MUNOOFZJZXZjbHkwZzZ5THZLQWxOV0Q1empqcVZuVG5EVXVtY29kOGltYkxER2xVc1poYTNUcEFkSW9rNzZkV3BJUVF4T2dMb3RIS2xjaXVCTWZJVnJQd2Y5UEpMMWFocFRINkp6ZW_SAbwBQVVfeXFMTU1RaFlFRkJCZk82cmVXR3NLelhiaGhFRDJhaWpTR1RzamFSQnFDcU9aaWxzclhyNjMzLXVMZTA0SXg2YWtoN0RvM00wUWZ2Vmc2Q2t2RXdYS3BZaHFJRlNVYlpvTF9QS2dlZzhwSUJ2VjJRTmo3c0FZX0R1dlpmTy1mVjloNk52LVFILUwtb0pjVFY5dEJMMzE4X0ExMTBSZTVNVlZhWlh6eFFsZVE2RVVoaTZmaWo4TWQxY2E?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2264,6 +2264,28 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>La guerra total fracasó en el Cauca… y la Paz Total en veremos - Indepaz</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNdUhGNHloeWdmUXVSTUFneXAwbkJNN1g3TVgzUnU1aEtiUHpqUEo2UW5CeTFyWEQyQjlMWWZtQ0lhWkU0emxTdG94Rk42YWhCWEFIOEhVaDF3SUNNa1FsYXlERmxCQ0tuRUFidWJkN3doN1Y2WnVfSzBsWDlndU9nSXJYbVFqTzJuQTJBT3N3?oc=5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,31 @@
           <t>Link</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Proceso</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Resumen</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,6 +484,11 @@
           <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQR0ZWWWZCTURsRVZESGlFc05xc0sxVXQxR1dSNGhUTHQyNHZrdU1RcFJGUmJkdjlpeFFkUFdLdlBZbmY4cy1KLS1QQXp2VHFYcnhMYlNSSUdXdmYtYmc5dWl3WThfeVp4TVVEUWdKWmxfc1V1MEwyN0FCYm9VUnVUcTFvMFpMQ0QwWjRZN05McUxhUFQxWHZraXd1dUVSZUhlWnBlV28zYVZKU0VWYnFiVEhuandNR0FHYjQ1cHRUZ9IB0wFBVV95cUxPTmpBeUVxTHU0TEpJUWEtMWFpdFZza1ZPSVdUU01sZHVWRU1HMHFOcmRQcjdOVXZ1SF81VDl2cmViYTl5T0FVZlN4dmY2OURQeHoxY3FIVzFocC13NC1UXzg3R2R3MmZGV3BzT1FZUDlwR2o5U19QRm8zZ2tyWkVvWl9KbWVrZ2wxVHlDbUhTNE1NV013WmJjRGZOMG5kdEgyZVh1S08tVXBQbUJRai03UlRtakxEb3hDMmkwMndnSGNtVmZ6eU5YM0VsT042eHhTY19v?oc=5</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,6 +511,11 @@
           <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQdWZ0MWo0WmF5MmtncjJVZWdCYURGanhfekpRWlU0Zmg0TDlMeFE1T0Ywa1BiNGFha3V6VmRsOTZxU2cyOWVTOTEtUHpNdkNGX0hDTkFQX0VYX1ZITDRibGhUYzZ4R3VzNERlRXFzNE5raE11VlMxNWFUbDVzM1pUNzVFREZrdS1WQ1lPOFMtNXZLX1lCMjFR?oc=5</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,6 +538,11 @@
           <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1fOWN4NkZ3NGZkWDNDY1kzY2NZeGp5Tnh2aTBabGh3cTRaMmIwOGcxQUFCQTZfdzZzbVdsV0JZZ2JrdC05ME1maU1LUDJKU01pVWxmTXVsOVQyazc4U1ozeHZlaDJGTTRsWlZYdWwyaE82dlnSAXhBVV95cUxNUXhLdU0zUlRyRkVtbG1oZTJMbXpFSWVmVS1FSHpVdDJyeFI2b2dFM0dKTTM5SGJZTTNEOGxlU1N5ZS1Nc1RZUXFEQXAyQ2FPMjdhZ0FhTkdOX2FxempDdjl4Qk1SNnZvN0JmaTBnQm9jUDNOc2ZCMFE?oc=5</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -525,6 +565,11 @@
           <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQbXR1VU9KU1ZOdjhqRm02R08wb0UtUXBuX0JjdXkwNDlnUFV5OFVUTUlXczJvUEdyRHhzenpXN1dWejRpLWgtNVhVM2JNUk94Vk9zYmxhR2lZWWlMX2poUTBFU3c2dEVtZFFBWldYeUJnSXlkd3pPWlAwa3VGQi1hU2c5TFBqcmlEWkE1U0RXZGdDQV9TVEVCeHNZZXI5Z3h0Y3pObUZCZ0Izbk1VUFB0NFVkdVZ4ckxUd1lKYVFGcnZpdER0dm52VWVyZVBFTEVIWHpLRWVR0gHwAUFVX3lxTE05YkRxQjFJLTdGMzA0TzRhazAtYkxYNThTTmhiRjBGVnVCdHVkY01TaVgwVHlKbTRpWjJtOXR4TWdlQl9EZldTdUh1MjJuQlFFaE90ZDg3LUdwa2pQMTdrajBDcWdqdE1oNy1ieUROeXlEcjJqV0xzeE1jOUhSRHBwdEx1cW0xbFM5Ung1RUc1ZUlkampJdlg5VHJCQkRtWGYtY0QwTk0tZDJpR3hWN21iTUttLVRXYWJzcUY0dG5jLWJHRndobThmTERBUkhHcHVtWVYxTm1NNHJkdEJVNnh5WWxNamZFNHFIVWh4Q0Utbg?oc=5</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -547,6 +592,11 @@
           <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQY3p3MzloSmxfS3h3dk9TUFo0ZkhyWkVQV3kzaGtsMmtBVVRMWkhQOG1ScDE4RVhNMFRXd0FVYVFrOEptRUNYbUJNd3NvakRIaml6Z3F5YTU1dmdqOFV4elZ1MUM1Y3l1OFVncERldUVSMjBtdVg4RWY5d2hFMTJZajhVS19sQ2RWUFU5RklsaTY4UDV1VlB0VWtVdGs5UGlwRl9mbEJZVTFBM1F1RVhBdUVFZGQ0SWljRm9BTENvT1Z3NzNIUFNfX2pIRU85bUd2aHFMcDcxRzNQUHUxUXJPZk56RFN4MVMwc3FxNmhsVXRrVF9VbWfSAZACQVVfeXFMTXp1dl9vcHdJMXR4ZmJrazZMSGJCRFdYalRpT005alZjMTU4TmROMmF2c2hydjh4Qk5icjhIeTk0Yzl6bms4RjRuWUdPMHpLdTJ6NVhKc0FKTVVybGtaTE5TekplZzNYb0NLNjNpTV83M0xqQ3JSUWpjRnozUUhEbENLenBNakFMQlAyQ19SSmVNZ0tKa3loZEpXUlFxYmRuRzc4RHFQTXFZeVMyVWxzTm5nSy1fX0o4UDBVdENJTEtGMzkxOFEtREVQN3dFZFl5X3JpdVpOWFZRaEh5TnFrZTVraWxLVkVzb1kyeklsZDJqRUlJbzFxbGlabUJmREpVQkZtQzRkM1hPVVhfQVNST0k?oc=5</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -569,6 +619,11 @@
           <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPeEd6eHViSkY0VVdoTmlLR3dmTmlUUW5XandWUHUzMnp0Tzc3RllSN1JmWkpVMnhLbmVNczlRMzBUQ3NCOVVKQ184cE45X0tHYzh2Rlk3TEh0TjlZS3dTX0Q4aWdOMHZlcHZZMERkMXFjZ0dGWGl2M1pKRFNCU0hyVWNkMW9scGVKaU1xTS1fM1N3eVNnbUHSAZYBQVVfeXFMUElHMVZTandKbWp2bXVRVWNnYTFsWXdWdnMtSVpvRG1qLU1BLTEzSVB5MEdSVzJGakxUemUwMFN3QWJST3o3LWpza0RHREl4eUxqOU1udVBNV09aVHZZdl81ZnRkVjQ5RUE3YmhhTnYyZHNzNHExRkw2ZXdzLWZTVVlvRHVNb25oS1VQbmRLazU1WGgtdHF3?oc=5</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -591,6 +646,11 @@
           <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFA4ang2LU00U3htZ3U4R1l4Y0ROYy1kNWFucE0wRThSWEJSWUJPeFhWYUJrdHNWWXVOcmp6dDFETFd3bGRyYmVDRVFvUzFmUUlURU1FN2JyMEdxUQ?oc=5</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -613,6 +673,11 @@
           <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBjT3ZiLTViRWhDMDdZYy0zM3VDd0tTN3NyQV9JYUNKWFpPaUt4TEgzT2Q0UDBnNjN1bzRPUFJuT3lEV2hlcEVMXzFoMzlDRmh6UFQ1bVRPb1U1Q0pCWjEyRUNLSW5NS0Y5eGpGZHdZaHQ?oc=5</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -635,6 +700,11 @@
           <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQaS1EbUpTeFNWdXIwbFlMdjBDX01yQUY4T0pXTVU0ZlVHQkZwYlBnc0IwbFFTNl9zRnQxRlFxSEg5MzRyT0JNN2tYV01KYWpQQ2VKdDAzdWFySFpSZnN1eXR6bHh5RUp2ZGJXS1U2TmQzVExQTnVHWmo2MzRmWENaRlVhdjFlOGtQVUxsWVI3TzZpdl9TXzNuWNIBmAFBVV95cUxPa1BjTnUtM3dYNlZDYjdYbGpxcFcyMnJEUlk1bl9KT3Uyc3dad0kxNzR1TmJYRU5qRWhmV29LSl93Ui1ZWjg4Z0Z6MlpGek1RVDNJX3EtOTl0RWpIaVRobUtCZGV0dDhjWktzR3FkanlIaVgwUjE3RE9aY21IamhhcUJnRk5hcWZycDVVb3V4WHR6bk5NQlVwbA?oc=5</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -657,6 +727,11 @@
           <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxOY3pUVWFFSk9lSEpxZUVNbDNBUl9PbzQ2aTRKcWJQWHRzRDBHSTRMVW05ZXdzSUFIcXJyVXRmM0RZNDFXdXB2M3huel9ZX0dENk5oSnpTUDdmaEtHY1BhTS1uaFZwSWhDWE9Jd21rRUNJQWpDWUdzSi1LRWVnZ2ZXOUZkTG5qVm9WajU1LWxKdDdHdkNwSC1PbHBLd2ZkbFQxUFZKTEdTWEoyR3FMZzZNMWxreFBsajdkUTVDMlIwYjRiZjZ3UWpDdW5UMWxKSEFjZlZuU3pFd28wSXNWMlBZLXZnTVBtZ25NQ19kYVdWdTZrazBIemJBM2NXclJGMXY2REVWaDNZTFVWbEt5SWJrWTF5UEpLYldNM3FmUVo4N3pwd2J3TVp2Z1h1dzdoOTDSAbQCQVVfeXFMTzFEOE05bkFJQ2FFMnk3Sk4tWS1BbnlzRnBaV2lVdFl0M09vejJfWEFPNklCaTktdXRwMlNDN3FYQ1pHUFh0R3BvaW5LMURqMk9xbHFPMzNWWmNvU0g4d19BMElmNmtTaXR3Q2FPRV9kcFgxNkZKaHNacm91bmNINmdnTG5MbkhHVWhyaXhVcWRyRF96bzUwM0YtTDJBWmlnLUZMYXVlRjhOZHZ6a014SjFfTnNsUFVkOUo3TGFIRF96V2tpaFhjQUZMMDVCdGpJM1F5Vjh6UkN3dm1FLTNkUGVEMmdqR01BbGpsOWMwdnlucHB0YlI1R21PcU9MQ1FqOG0wcnZUTXZYcmdOcnNsc1FaUVpJVGJLR0JlQUdqc0k4bTdSejJZU3lSdGhhVmtpNTlqME8?oc=5</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -679,6 +754,11 @@
           <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5veTNXQV9DbUhGNTlWLWQ3a0VhZDNXc3FJMzRNTTBidmZPVm1UYjlfVDE4TEdtZXNNSllLSGlqVW51ZHpBcTc0UkpWclJsV1VnOHBrTFRFUWdEYzBY?oc=5</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -701,6 +781,11 @@
           <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5LNjRQU3pnMTMyNmdVdnZiVS1PYnExbXhBTU5McHQzblJYV1RXVW9hZ19VYlVMc2JfeGV4SXVGdTVwd0x5aUZQMlpYWUF4a3ZkZUN6TTlQLS15ZHZzTzRn?oc=5</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -723,6 +808,11 @@
           <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE14Yk5QR3ZjaklxcEg4VUpDQ2hyaE9fbDRPQzM5cUhLc2hiaTlpOUdneXRNUWQxQ3VVTzh3a3VuRGVPNkZERXFmcU1wSEp2ZUt5amZYdFJqZnJvNnNBek1NMmJCM0xMZWo2UjhpRjh0YXc1Nkx1?oc=5</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -745,6 +835,11 @@
           <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxORjNLbmJZTVdJZzlGR1ZfU0FXOXdGc2pxYW0yR09IWW4yTkpmWUZXMlNqRkxqRnJ5bVdMalc5YmZPc0ZGdmxmUUZ1SUtjUndyTmhJVnYwVzFtdklQaDhiNUsycThxM3NrZkZBOXNaTGIyU3plMGNRQ2VWQ1lhMGNveXFrUTE0MmgtUXc?oc=5</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -767,6 +862,11 @@
           <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNaUIzelExbEpWMlYzMDZWdTR6Nm1TTFF6OEdpdmI0WVM1THBXNThrbFg3ZXQ5Q0JNd2RVN3RXSjQxdURsMnhKbVBTY2x3Z2pQZk1qcmg3TVFaZmJkRWZjRmVXdWFrWUlOVGpSWlo0YzRKQ2xtV1VyX2dPNnNUUUJOWXNUdGV6X1Y0Q3c?oc=5</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -789,6 +889,11 @@
           <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNcHRiUl9fVmRrLU1rcjBKaERjeFdQbGxWYUN5YjBoaXRVTlo4SUt2N242VG0yYkdiX2tyMlViZ19XdS1PeGlTcklocVFZOVJTR3R1bWNzUXJkSks0cnNlUlpKbkhqS1MtbWhtSE1mc0I5Wk5Vb1BSeDMzWmRHR3g2VUNGVmNEN0FSVDJ4U1FtUDdydHcxOGc?oc=5</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -811,6 +916,11 @@
           <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9PNkFHWkM4NExmNVZKa210RzVPa1B6Q2FMTGdxS1hDNVlnSUEzREktU3VVR2xXZjVWV1RXWTRKdXBjU3ZxUFBTenBaQUdUN05NZ1N3YmQtTnFVMW5nb3Y1U3M4VExMQQ?oc=5</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -833,6 +943,11 @@
           <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1lWWJOaVVIaEN1N0ZRV3pGSWcyMy1Ca2l2UmtPcURfVGtWdTdCa0pjcDZ4OWV4a3dvbUFrT3BsN2lYZ25SWVNFQjdRQTlEX0I2c2JwSVZKcmhEUUYtYkY2MWZjMA?oc=5</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -855,6 +970,11 @@
           <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPaV9TMWJxNzBkRG1ZQV8zbmlwaUp3RTQ2eVVDYlp4ZmRvRnVSYWlFNFR3LTBtRklpU00wTnFUSld4VFVQX0w1b09rcFBqS1lsdmdlalpsVDA2bEN5aFZsQ2RGVjdZd293bTEzVlJNSGxPZnNjZVlkdUc3YVBTTFRlcFZNRWNLX2tPTGc?oc=5</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -877,6 +997,11 @@
           <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBxdTdNSDA2M3h5YzdFYTlqRElLaXRBemh5alVTTXBqX1V3WVNCRENzSUdZU1ZyVHY3ZkM5NURKazBpMXh5Q3V6QlNORzJnajA1QmEza05JV3JkUHhEdTFXU2puYw?oc=5</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -899,6 +1024,11 @@
           <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxObWw3WXVDZU9GN0FwUmJsWmVWaHRLdzJxenk0N1U4XzVpRmlwUWQ1dWh1YWRMcXBLNWFtQ1hwNFUyV1o5S3FoZzZwQ09FZGh5Rk1lcXpBLUVIZU1KcnFKYnczUmZhN2NWZ3pXU19lSjY1LWlubE13X1dic25JS1BGNXowbHFWVkNPQzUtc1BoTGVJUFVoNzRULXZ2Q05FTkFLODhJNGpxeHRMbnBfLUh4TUJyM05EcUdVTW84SmZUTGhnalNfYk1HSHFLUmRZQ0pjX3g2Q1VyeVZRVW5PMXZTNEhmSjdLckpNdWxnOEo2ZV9nb1lXSnfSAZACQVVfeXFMTjFrMlE5VUY2Rm90eThKZzlNSjVFNDB1NG1zazd4SWJRLTFVWXVGVjlBdy11SmVxeDZfY1pqVVozNC10NzYxajJzdEdDbHhlUndoUVBHTUFwQVNVcU5XWlAyZTZaLVIzUGZqRE1kUjhEXzJhdnhCUlJFMkdJTWJmdjI3cng4eF9vT01IMlp0TFVxWjNhRkJ0LUo0SkhhM1A4YTZUSDdZTUpDd3RHbFdmaVlPaUFfX2FqZGVKUzBjd0FyOFZJWFotS1FCZjF6eHNKZGRmdGltdFF0YTFRZHVfZ2xKRWhwdDZjd3JjTTFnTDJ5UWY5Z3A5NGZBNFB3OC1NY29KOFFMTWhHaWRDS1FUU1c?oc=5</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -921,6 +1051,11 @@
           <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOczhRZ1VJc25jWkhTbWZHdDFRMVpJcWdUd3VNY1VlckRCRVdPcm1DT1puMmpKb0lQeGctLWpmblZKYk1fN1Q4QTNENXNlcXdVOFZ6c09EZjV0anRfMng4TkZ4SnJqcjNIN3NjdUNTdWh5SWRwRFlMM2tzRlNodXlGUHRwMzNtSmo2bkZvVnYzcVVUT0RtQXdaSUNjcXNvTWc4eWU3RlhTQ05VdEd4aXRnX3lnTVRrNXIzOUhNWtIBwgFBVV95cUxNeVBubTViTWdSa2l1dGx5bEVsbEVpUmh0c0J0cmVYNWFxbllDZzF0b0I2Yk9vTS12OW81ZnA1Y0tHbG11WWhrX0txNHREWllLYWx6Z3hSaFJNN0wtVjU0TWhLWkZvdFBfU0xvei1oTzlfQmtGRThtOVNfZGxodVdGZ2loNS1VSUZrSmxYNGMtdnpqTHM1ejRwWFRkTm1WTjVnOFBJYTdiLXRuSUlqNGgwLVVPS2V0Ukhqa0I1dmgwUXZuUQ?oc=5</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -943,6 +1078,11 @@
           <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQTHpna3NhU1RFZ1kzOWZaUmFLTHppMl93MzVHeTBmNGR1MW1PRHBRZDZncmxZTUdTMXFDOFI5WWY0N2RtYmw3RFRlOGctV2s1bmpZY1Nhc3BTZ0s0Um9iZjJWSjFTdGRBVkc2ZENjOUg5b0d6RS10TEFiWjdGVHI4b0o3TTcwMVRfb0l2V1BXMDhXcVloVHpOZ1hvbkoxNjN0MFBBMnVNcGpNcU0zR0E1SFJvMUxiQ2NzVFpsejhydU85U3hhcnZBU2ZzRjhnS0hnVWxyNW42cHprenVvNzVma19TcEtZc3pOemVRV0lKbXREVWZQ0gH6AUFVX3lxTE9PUlhkT2hRS0EtZXpyZjUwMFBiZGwxaGNlMVZlSnJ5Y2E2OXlJQ05udE9xSzFLd0FlaDlQb3Q4S1EwN1l3ekUxc1I3bkI3ZlFrLWxwU09nYUF3TE5WTW01VUs3TUNGaXJ2ZXRCTjdtbmRac0loTlpjWVR2X04xVF83X1BUelJ3UnZzLVRhV0VxU3h5Yjh4R3V0NlIyc1czeHN6QWc2UXUwTlhsNXBmQWdaREptZUJEcXNlbmMwWnJuZG1WYzNKajAzbGZscy03emFqaTBlUTFxZmhhZkl2LTBaWGUwYnJzNnpGSlI1cFFSU2kzbUVaSTJrWEE?oc=5</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -965,6 +1105,11 @@
           <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxQdmU3Q3VIRjN1OUtCUjRFdkJXakxPdEhUWVFsRGlQVVhWVE91ZVpmNlRuUEttSk9ZZ1licFFsdGUwSGZ1enQwMHBkRk51a0VkMmpBVERDTVFkRzVMMGg5M2ZUY21TS2xwV3ZmNUx2Q1E4Vi1ERFN4ZU1UVFBTZ1VnSHVhWjd6SHVLeF9WMVAyQkJJMVhRSjRLdW93Z0x5MW9YSVVtRlIyaXJjZEhVZjdTa3BKS0hid2JRS21GdE5FLWFWN1kyb2hpMjRsSmlEVVR0QUVCWVRQUXVobmlUMkxJWjdQT3ZtajJkQ0Zid3U2bnpfUkFQR0pVSkg5TUVoZ21IWEpyNEN4RdIBogJBVV95cUxNR3RESFBiZmxfYU5xOWJNdTdfU3VIbkJTbHdpTmIzZEQ5YmVWMnVmZ2lNbTNRMmEzQnI4WEUyUzJZY1ViUVFCSjRDaXFVQlBGSnFoYVRwcXo0YkRhZEtsOS1yalhxMzhSdFFzR0JhN28zMkRmSVNmazEtd2h3UVNIVXRidWRyeFd4T2J0dXNvSVgwNndfczVnNEh1UEVmejY5ckpSUDJ1Tm1JbnFnVWdUN3d5R3NEZFhyZzQ4WWJXN2JEcWFUQmlyX1hSSDRoMzdxcUhGRmRqWnM2b0RuSC1ITlktTTdBanV1U3JvdTZWU3BDOWR6ZHdmVS1vWXRzaUtLOURaNkV0VTVNRVROSklINkZtYWc5Sk1kdmJOR1VOUVBJQQ?oc=5</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -987,6 +1132,11 @@
           <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPOE05NjRFNnJSWUlXTkNoMGVlZWc2T2dTVE5HYVA4VDBodWdiOWkxLVllSDJUUEl1d0EwcnZqTEN5LW9GUDh4bzFGZ2ZJVzEtdHVVbk9XbUNvQjdUcTdRVjNvY2pqWDFqbzVyclpVaGotaEJYY082RnE1ODRvLUp3elprQnBxcVVMNkd6X3BzMmNwZjhSUjk5d21VR0ZJTGo0SExvLXUwZ20tdEdTdWFPb2phNjY2WUFDb2lBaGl6Z2VyM0lHbVJOekswd0dVMVh4Z2pJbFJBYzc5SUdFQXV2YUp5RDR1T2thcnphM1BLbmU4Wnk1YThMcVBsONIBgAJBVV95cUxNbTJPMHNSdllaX0J6aXhpTkxCTHYxbXRqa2pWcm9NUHJ4dUI3ejNJVU0zSGwwM1U0bllQa0Yxb3pCSEtEVzc0cjVCV2FENFdSdExRaXMxcGRLbDdFWUp2OGxxU2x1SjJ5UHkzcl9WV1M1ZDU1a09aRHpuZlBSREExOEVBelJwSlFfemRZQVFrVktGU2lTc09XNk5HeDV2cnhSY0VjS0k5b0tmQ2pwQ29kOElfUnlUa0VPN0VxS05zS2FNaWlXUEdack5CVWctQ1RhNDdDbW4xYmEteDI0LVJHTlpoeWkyb2FQUEh1TGJWczVabXQya2hWRVkzc0FOTWJq?oc=5</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1009,6 +1159,11 @@
           <t>https://openalex.org/W4393090309</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1031,6 +1186,11 @@
           <t>https://openalex.org/W4328127345</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1053,6 +1213,11 @@
           <t>https://openalex.org/W4409047917</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1075,6 +1240,11 @@
           <t>https://openalex.org/W4400907389</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1097,6 +1267,11 @@
           <t>https://openalex.org/W4411200418</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1119,6 +1294,11 @@
           <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNdUJybFRXNlA5VVpKNENsTmpkNGhLb0hkcGk2d0dpZlNLX0JjT29nbHZYTm16dG9ybFFwYjNnMmpMbHRmY2UyaFFWbHJwQ25kb2xKOC1GQ1ZzNlNERV9YZy1CNG5HQ3RYSWZfenhVajdGMkZ1QnVtd0wzSXhiTnlNc2Y2OG16eDRMYmlyNjdBZXR3NUZHc2MzS1FxMXc?oc=5</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1141,6 +1321,11 @@
           <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPdTktS2xiQWxEV0wyTlFzX2Y4Q05KRlZMUEtRbWR3VDVZUWNkX2s1QlVIbUo1ZHFhenI1VXVtWVhGZFhzejlhUHJxcWxIeTZuQlFmcnRoNmp5VHdQTXNhUHZsbldqWjhrMktkQXI1SlBuenhwd195Q3c1MzF3aVNPSEFJRzJHZ3FIelBfY3lVZ1BWRHVEOXJRZWZlN0ZmaWEtYk55d1FTbVhGVUFaSExNYzBvYzFLRzFxbHdqeFBPaDZ1Uk1sR2l2T2pJY0l1dFdFRUE?oc=5</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1163,6 +1348,11 @@
           <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBwRjBYZmlMZm0zQkJGV1k4V00xSExjR25CSGlUdFVNR2dIRDFWQ3lWaWtFdGdURFpyc2Npbm1wUGZpREFzU1czYkdxQ3VDVnp2UFpVaEZKMk1NNG1FRUNvX3pyV3R3QXk4eVpaNA?oc=5</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1185,6 +1375,11 @@
           <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE91ZHFmOGYya3NqQ3I2aVQ3dWZXNHR1WEFrTndWUEZRNGIyTENucEc5eVBCeHRweWoyRDdwSGk4MUVUajcxenNYV1dQd0JWbHptRGpKV1VWTkVBT0hlbFdGXzI5RmtnRTZXUjlfZg?oc=5</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1207,6 +1402,11 @@
           <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9xek8zaGlrX0tmRUZmSEFWNGNzbmo5dmZjRlZQZmlWT2JodGFvTS1qaWJGa1R6dlZfdDdyQllwRFRlc1pyUnktTnVwQkl1ejBEcVp1S0V2RWgyaTZwMnpOWGtxRG55TDRrZGlZ?oc=5</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1229,6 +1429,11 @@
           <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE5QMFNTd1E5UzFmTUZ2eHZCbXRuVTJDUVpBeGg4dUhsVnJUUUJFbHNmczFreV9qMW96T1lOUlBSYWxTMUtRTWRtZnJnTHgzNDRNRUhnV3lya2IxRUN1N1V5RGdVb0JsTDFuNHBF?oc=5</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1251,6 +1456,11 @@
           <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE80MHFWdXJGTWI3MmU3ams5bVVhZE01YzhvQWo5ME9MODJ3b0NGRDZpVHFaQkE4di01Yk5DWkNqa3l0bm0xMHhtbHRUZTAxWUIwdVpra3BVTU9pWVJWVnJycXlYQkJibE54eGFocw?oc=5</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1273,6 +1483,11 @@
           <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9PR25oalM4N0FmVHB0SzVkSGVZaDBVSUxOZzJCUE05aDk1ekUtM2ZfOVNlUkdUNVFOaS1mYlJoTExTamZxS1RsUnp5U2thQUVDNDBRUk4tNjNPakZrd0hwd2tqb1hjNklKQkNBMQ?oc=5</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1295,6 +1510,11 @@
           <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE94bDJpZ1pYVkZ1bTUtZzBmOGFXZ0gxTXhfcXRVRkwtaFp4c3Fhd1RRSExHc014Ql9VM3Y2NGZJOTdFV0dONmJOcVFBVjc0UW93aHhtUDFfNTlHWjUteFBLR0FMeDZ1V19kZGVEYQ?oc=5</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1317,6 +1537,11 @@
           <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQZ29EbkN6eWh6QUROUzNJcG5hYURURGROSlRsc3RkWVM2MGRtdGgyTGtwUHJSYjdLbTRzVnJnaW5tYzBVcjluazhBalhWUXF4WURaa0JnVkxaT3VOOXBnUWVTTTRRQy0yMThadktCQ1dMSjRWTUV4Vkw3Q3E3bG1NaXJscTRvRTF0ZnlJT0JBRE9vUndNRUx0TTZBcWdmd3dMd3VnU21YUVbSAagBQVVfeXFMTjRIMWtMczliUlRDaDdwNlhJamdtdnQxMERTcS16Zk1WQnMwUEFFYVZuUGp4ZTF0dmhld2dMbWtXaUNySGhRTXlKUi1ablNkWmFKRlNzUzFrbmVXMkNXN2d5UlNpbXRPclZpb0ZCVU9LWVZSZDlOVkgyQTV6OVVpeS0xcmZ1N1hQMjJfZHR6NEhmVXI5clU0Y2F5dWtWN1Itdk1HN0YwNEVf?oc=5</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1339,6 +1564,11 @@
           <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQSFVsYUNXRm1GWkRGQkpiamUxWkJkQmJNa204cFluSHJqU2hwQmMzc3k1bVd4aXpLNWZEZ1BxT2lacmRGbXBBLXBNVzluMlhhRmFoLUt1M3BaV3BiYmRZcjM4VkNrdVYyOHdfTm5Ta0I5SjV0U3ppcXhvMzVWeU02NzZpV3YyV0IzZWR5Z2FiQVI5Z0QtUHItY2hIV0xqUUJ6TVk5bTJNc0JPRGJMcXI3S1dScW1mV0YtbndVQVN5NFNFdGNSQzZ0Vk9WSnIySXdwY2QzLTlTS0habHo0ODZUSTl1RTk?oc=5</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1361,6 +1591,11 @@
           <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNcm5aTGdMd19EMUliZlhzTkMwZkdfeFQ1c2EzZkRLdTNSTnMwNThTbWhRTjEyeHpNajdrQUhPMk5YN09lbmFOU3V4ZmNEZTJCMEtMMmpIMXdZeW9hcldjOUFXNW90THJwQjRXSmRiY041ZXVFTkZfQk1MaHpPeVd4UlBRcnNaaGhzZDFPbHRVcUxya1FzcG5oSzBoTno1clcwU0NES0RHczY3RFdHbWsxSXdyOUQyMU03OElWYWNDLU5pS3NtSDJSVmdsbW01RWR2YTBmS0tRQzFwdS1YYTIzOWt3?oc=5</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1383,6 +1618,11 @@
           <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNZUdHM0dWbTU4TGZiMTlrVzV3TWhhcE91X0JSWTNOTFhaT3FZMncxTjNBMm1mQnlwTHUtak5fR0xwMnA2LXQ1bW55UTBDaDV1YXlIcEJQTFZUV05GQ0FuTUo2cTVmWGtXNjFzWEJUZDRib0pMcFZmMDNWby1zSkVqQXRjRDdoNzBhaFE1Y3VnaU9TWGlkMGdfdHowWm1IcjY4Y2cweFNJQTBEdGhHbjZYLWU5Y2JUWGJPMmNFeTBrTVV3dFl2?oc=5</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1405,6 +1645,11 @@
           <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOWUdXRW9pMkN1dU1OUVdPckFYdThHR0VYUHZxbkxOUGpaV25XdWxOVGF5VnBrVUpfVWwtenYzTW9wYjMxWHJ0RHFITVNBUThrbG9sV1JyOWJTUzI1M2pGenpmQ0xsN040aTJzVEVWZTlMUk5XdDZsbkJiSVFQTHhxa1pia3lrTmlwR3R4QWYyVFBKdVhwRjFvWEhWT2NvcUdmbWFjd1k4UExwOW5FZk1fWWgwSmo2eUFSTjRKbDZLNEFZclVxNUdJLWFkUjc3WWh2WWc?oc=5</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1427,6 +1672,11 @@
           <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOVVVpSmlNbkE1SVVwdmZzM01fSllGRmNWeXUtQWFrOXJuT1V1b0JFTzRweDZXN2h1cmJ1UFA1dlFjMnpsdkoxQnA5YUc2Wm0zYldzY3ZJODNPWkVRekRWYWN6MWg4Ql9KQmdNbU9DdUl1RG5yNDRhcmFDN1NOdGFDS1U5NzJiSUQydV9OUUxyUzYxQXVDX0RwV0pzbUJwVHcxUU8zU1pqRl9EcjFBV2xOT3pwVTRxbUZyWlh5MVQ5SXAyVlVBVkhpVmNwTFE0Rms?oc=5</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1449,6 +1699,11 @@
           <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5yNHZfQnhsbHU0b3pXUmFCN0ZiSnV2ZmZvY01kdzE3eXBhQ2FqSXU0TGl2ekFWa05wWnlYX04wZWF4VGJaWjlGYzBYSEhpLWxxMXZaa0Uwdm5XdXFOVXVmVHZYeEM1dzJoQ3doYkU5dlhKTEE?oc=5</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1471,6 +1726,11 @@
           <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxOWXFZYURQdlhnWFlwZFM4T2dza090UjhtZ1hYWkl3QVBnNUlVdXk5bmNVTmkwVXZpVmJQX0xvM2JzLWljUzhaWVhjdlpXUU90TndzV0dnVFVhTkluekM1NVJUc3duODNRX0lheDVoRG1iMnJWc1hieENqYjgwdk10ME9GNHBVWkI5Vi1HWVV1dkpTZmNIdUNyUXFpa2NFbUpudWtHVnBfa3RSUmgtRVNGdnlQaldhT0NDalhCc1hPbkVSUnV1T1BvRU9mSU5CZjdoMjFKUTFfR01fc0Uwbnp3NGdYYlY3aDVseERGZUJUNjBaVkltZXRwUVJENUdmN2dE0gGUAkFVX3lxTE5RWVJPMUdUbWR2Y0JXdWxJR3lvdlJqa2VKN09TQ0VQWE1idzlfdU16T0M1SHZ4VVc4UzlzUXRocHRDOFVxX2FWMHA2UmRpUnlPbnB1ZDhnby04b3hLZXl1WS1PTE9FVXNKTjJGdnFYSGwzN0dZZWFQbko3RU1XZkRjWTVQZ0tVdC1HdllHMGg1a1IzYWFEVkpJM0FyLVN5UXctZGpIbEFZazRHTUVPdDkwRDNweTVDX3hMYm5BZ3hsR0FRVXltVmEycVFMQnZrWmxqNjljeTNCTEZyVFBJRUtNVnhOX3ZsdWs3b19XdTFlU09fUVpJVWxqcVVfd0RKbFlzdDZZd2l5Z095all0NEUtcXBwbg?oc=5</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1493,6 +1753,11 @@
           <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE4wdDFlMS03RjVGQlYzVjJ3ZWZ1ZndzLU5UTnNseUlKeHdocXV5NGQ4NzEweFpEVURtNUF5bXR0eGduRzItS3ItNjNTR2VYTWowd0FXVFl5U3BNNl84MklaedIBYEFVX3lxTE4wdDFlMS03RjVGQlYzVjJ3ZWZ1ZndzLU5UTnNseUlKeHdocXV5NGQ4NzEweFpEVURtNUF5bXR0eGduRzItS3ItNjNTR2VYTWowd0FXVFl5U3BNNl84MklaeQ?oc=5</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1515,6 +1780,11 @@
           <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQekhCYXhpLWRsTnpwaXhhUklrNURzMlQtbnhvdlB4U3hsbVNfSnJZam11QUtjaWJuTWxhbTZwTHVHWU1yZHFSUm1sOW5yZ1loeTBMRTRCRlRDMnBPMjRsN0pIR0RfM2FOREFUd1JpeTRDbmlDWF9xSXVDRjhiOHRCckVWWEFMR01meHIweUxCeGQxdlY4dU5oUG1IeXdMNV9WeW9pX3otc195RklyekRHa2U2UWJodV81akxCY0lZMXF1anloUkQwOWw1QkxqdHppSTVHQjVWQ2N3Wk5hcTV6T3FLclNWMjVCSUHSAf4BQVVfeXFMUGpBaUppenFNWG45emFEb0xIbGtQQWpOUzhXYmh6QzNpTTZ6V2phNzNGVkNRQUpOeUU3WjZ1OVMwZkJsWkJLOWFpalBaVS04Z0x3eTdXWlhIWjFHd1h1TDNSQ29JS2tfLTJ3a1gxajBlakZDU1cwQVA3MEM1dEtpVXJKcl9nQzBjcy1mSE5vZ2JXVDhRei1MMlZSRXpGai1OeGQ3d0hlN2VRc0VRSVZOYzZUblFMUzAzLTJCakVLd1ZQU3dKSDhIMUlUNEZxUTZSUzdPNl9kTmg4Z00yZ2JtazVDeldtV0pkeDJLVllSaU1uMkg0NjhNYmZ4aXBjRnc?oc=5</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1537,6 +1807,11 @@
           <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxQV1g3WUFMZk00cWMxSWc5b0xmNUJUQ3RaT0dCNFlmVGhTbEF2LXBMTWZDUldVY0lYOUlEd0JWUnVJMW5WZjluU29wMHRPeDlPWWt6ODFkSGRISVlNeXhhQ1ZZRW50ZWFaeXoyeHpKQ083N2lSZEVjWG44OVd0NVJ1UGdoM2xCTWgySzFlWDZ4M3p3dVFWWUFudmY5NEJrM1F0LWZEY2tKNDA0bGczek5TZ29GMFkyWTlOSjJabFZQS3h2S0VNR2VtMnA2dU5iYzJja2RMaVhIZDlRbkNUMnh5LVFJUkw2U3VFdnNuRkh5anBpTUl2VnYzVThIZFNJUjZoTWUtRHVIRWhkZWfSAZACQVVfeXFMTzFmcDEtR0pxV0dxbFJVOFM0UlZBWFA2Ql9zYnRFbWM4UExIN1ptVWVpQ29vdHNtaTkwbl9LblpTVmVUS2JIdUNzdWFqbURIeW5yVzRwV0VKLXlqS3gxVC1vSDhBakMzRXNKUTByOU5VODFBMlFiZ01INHJrclpVdk5JRC1HMGV2eVo2d1FCQ2dyOU1JRmhUSmItdHNzNUZLT2ljQ2pPOHBMc0xVSzhUc2wxUWRoWmM5VzVWamlwUUhjaHV5TFB3b1BJMTVQRS1LX09ISzktRFhJcnlKdGhZSFVUSlcycUhKRF9jc1dpLWRrT3VBRTNMMzBoWkM4dFltaEQxUTliTTZhMnNkT0psX18?oc=5</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1559,6 +1834,11 @@
           <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOU3FweWtDWG53aTdEMUI5RnlaTnJIYlBhbW9USm0teHgyRllYZTBVVXkyajZwenZqSWhvX0laVzNjcHA4ZHgxUzNUeGE5QWVPaU9vY09vbEFpWENFZnBqbjFtWWlnV0lMR3R0aV9tUW5zNHM1a011NWdBLXZSYjdGU19FaWlRam9TcEhTblowZExKc1lVRjYzdlBOMHVJbkVPX1ozQXVua21fRVYz0gGyAUFVX3lxTE5lX1ZoaVd6SUJMMTM4U0RVLS1KY1JpY2M4SWdCYVdDTjJMUnNpdlZNUEZoSkRxZ0RLSkJHdWd5ak9ENVdZcURCdXUxLVgySEpveGVWQWxxRXlCam9RSV81R2dwdTl0NFZvZTB6bi1mZzRKLW9teWlVbWozZjVFZjRnek9GclN5UUhyZ1R5ZkdEZ1BuX2JLR0RTSk5HOU5FTzJDelVKVXlrYjk0SmhsVmcxV2c?oc=5</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1581,6 +1861,11 @@
           <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNNUw3WHhkdFZKeEE5Sk9fZ01KcUc5S0RSNmc1eDBfUldjMkRTbVdSRTYtcWZPMmlEU0V0SGU4MDJzX05IcFdCNHAwNy1XVEc4dWFqaDRma0JmdGYzcW1HS2xQc3F3blZTWWV0cFo1VFRIU3pFT25BZHh2RjRLcEI1MWZHZTd5RWpUYUtMRzdsaUpleTZtN1pYeUxsRzJnQWRGdUt1ZGhKcDFNRmJKZmdPWW8zcVVsQzExcXVXRmVOdmVKaDNVbVZSakNheU1wako4eFFUUXlNQ0lGNkpGdU80WE1vekdYcC0tNlJiU3E4b2hOY01LUy1DRFFhdk1wVkhBcjFTZGtOONIBjAJBVV95cUxNdW5taXJYWlhJUUlxUDhvY2VacUdlalhDVjJDeGwtMWhiWkoySTlVOGRGdTZJUkV0SWxQNTY3N0dIWkhoOFlMVzVmakk5cnJwNDJUUTN1UDdVejMtQm1jOWFXczZUT1FhRUNuQzlteDYwdnFkV19ZY3hteTBJaVR6X0JMYU5rZnlmTTh0T2E0bWc2bmNrWm0wdFJWZEQ2dDdzUTN1RHNKWmZxcS1DS2RPMXItV3hacUE0UmlhMGlQbXBFV0xhOHhSNXRZT2oxc0pvdHo2d0VnX0lCdlVaVV90SWlUeDFvdmNXMVJ3a1VHTFQ2WU43cWFaOEhKQkNaUVRVMm9yajR1Q0pnb3do?oc=5</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1603,6 +1888,11 @@
           <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOcTBYS0pGOFVHZDVMUEQyOUt0Mm5ralZFTkhpRGVBLTlIaWlaeERPUmw4Y2NKNHQ5TV9ZRWZuR0pyLTN6c0dJTmhQMk1mNzRnQUhoSHJRYXJzRzlacS16UEUyeUQ4T1JqTDY4NTRiMnNHYVpncVBZWHJPTWppcFU0bjUwY0F1VU5pZ0ViWlhodC1BS1BfM1p3azZDM243ZWYzZnc4N1pkaGxvbjB1ZmRtMXFfaE1kdF8zTkZvQnRkaTF0MkhpWWl6RWRxaWVVOVRVTlAyZg?oc=5</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1625,6 +1915,11 @@
           <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOQU1QeFRCRmlBaWUtSHU3bF9OOGhDTDkzWUtYRFVCYkNMS3lmNURoTTJ2dDdOc2hsMHhVWTA3SzdRLTdCZ3gzZ1owUDM0YXczWGNZZ0hYTkFoV25sNEdqR0ZZSElVak1ob0JBeFdoSWN5YmV3Rm1heldEb0N0QUxLQ0lvR2NNbUg5VEtOOGEzaU9RN0pVMEE?oc=5</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1647,6 +1942,11 @@
           <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPYVRTOXBxWVZvSFRDSk5hWmdkRkZYWEdZdDMzcjFZQXhKZWNibDVKYnVMMlFDMTg0cWVVbm9uNXVlQ3prSGhpZW1rM25qVWNjUHRXM0xtWkd4Rmd2MVFHY0FlUk9pTkpJQ1dBbFJtVFlWYXBFMklEaTVIMHBSTkZTUE41cjdXZndkWGV6Ym1Jdnp0MjFwQ1FzVlhDR09RSF9jb3dobTRGZi0?oc=5</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1669,6 +1969,11 @@
           <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxPbDZLNFotT0RpMUVvVjB2eXFGdVp6WFc2UUdEZzNPVnh6UGVaLU9FSTA0N0sxODRXZzNIUno1WnFVRTJlenZpa09BZUZWOEo4TDFGczFuNnQyX0tRdTVRQU9tRV9FVDQ4YnpEdWtKMC1tUVdreFdOQkVkaG5nT3NnZ2V4dmpUQnlYcVVSYUgxM2JCbHVScVV5aDJYVVQ1UFAtcmItMHliOWpVYUx5eE1HTDhUcXVkQjlTU1RzUk5QMHpUbmc5dG1Fc3pPVVZRSzZVMzFPMFRka3VRZU5CRDJYWUdheWxPZUFSSHQ2QlE4SXNIU2FjTWhzc3ZIS1JJcHZyUy1B0gGeAkFVX3lxTE5PbG9PVUZIRlA1U1lEbTI2T1hvazBSc3VERGtkejd6RFNLMVBLaFJGWXlBVEh4cjNLTWNwMjIzV0s0LVNTbWJ1TS1nZzVidk5lSnU2al9pSnNqTHB2c0xJVE0zWWZmV3R5YnYxWFdZbFZOWU5XUTFxb09oVmVya1gtVGJTaGJVMHVWb0tpdnQtcW0zaHBiRkVValNrekZMeHJ6bHh2OUNsZzktNnBsSFZjblNwRXM2cmxDVklDb1NZSDhDZGlBZlY3ekF6WTV5T2JzcE9rVnF3TThJeE1uLUN2NUtUWEYwcHAzQ0hnMXY1b2Q0QzdpRzhOWEFfblIyVnlIQkpIdUFlSV80S09uTjdPUVV6TnR6cnh1OEF4YWc?oc=5</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1691,6 +1996,11 @@
           <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxOVHdyUTZsa2VadWp3ZU9pMDItRm1QWkl4NUduLUtfOHNVY0R1bVVHMnp2ZHhPQjFiVEJYclFaamVYVzd5cy0zcGlHYWdnenM2UExqclp3di1QbEs1RHlYS2lzVUZjZ0NaWFpDM3ZUczRPUmM3Njd0TnlieXZSX3dhN3lvRWV2TUhCR29DMUhNMnRRUFJxbUYxbGU1NnNNQVFyMExMNzBkZGNBZmF2UlozZDlCd3hFVDRQTFM2eFZLR3BhQkE1eXg5WHlhY2V3SDcxZlo2OWVwUVZfbl8tNkdRLUVWVVJYei1kYllEZ0pqa1g1ajYzZUptMGc4ZmNCRmtOcTluT0g4MW80VVRSaUVEU3JGbG8?oc=5</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1713,6 +2023,11 @@
           <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBQME9WVUJDX2hGdk01eV9oU0hkWW1jZXZnZ2k1Q1FQSFJOcnpoRU15c0V2cGtNMXAtQ3VaY3BZUS1wa0Q0dTJDSnJHa1UxdEFuMTYwUFBEMnU4eE3SAWBBVV95cUxOMHQxZTEtN0Y1RkJWM1Yyd2VmdWZ3cy1OVE5zbHlJSnh3aHF1eTRkODcxMHhaRFVEbTVBeW10dHhnbkcyLUtyLTYzU0dlWE1qMHdBV1RZeVNwTTZfODJJWnk?oc=5</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1735,6 +2050,11 @@
           <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQY3lmOXRrVkZVTXNfbVJ1VERjRHA0ZlNkZ3c2TkhtTFh4LUI4bmxVc0Q3ZzduSXJReGNYdWtnQ2tNdEZMaWVzcmhOS1hZWUY3LWhYdjFVMmdmbmhuX21PNXgzYjVrbTZTU0RHRDI3cGdQYzZ1Qk1KYlMtVXNpbDlMZHZ6YmJQNFJkMG9BY1Rwcy1XVFd0ZU83S0Q0REFQZlFDNnpYaUZFUThEMWxrTGlIcnFOeGEwYnc?oc=5</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1757,6 +2077,11 @@
           <t>https://openalex.org/W4300009529</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1779,6 +2104,11 @@
           <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQaUVyeU1VNGxBbTlfNFZsVGNjdWFybzBmQmN3U2FWaU9Vb0c3LUI0TE5MYmQtNUo0UGJBUUxONHhLbzFkbGtva2hlMWFKd1RFU3E3a2NqNy1HUkZDeExRaTJGTWU2eVdmRVJaSmo2eXVibFFYZkU0SHpjNlM3Y2lSUVY3Mk9TM001SWVEVklPbWR5MDVtN3lnVi1IQ3AtUTVBcUZsVkFwZnlEWlpwNy10aEtESEVyU3dDYm1saWtjcXhBaURPblFHMWFLd1YzMV9NaFVjSU5WNG9MbDBwQlpma1NnUDZBbXhhZ0MtX2VybzQxeG0zYmx3dVNLRkJ6XzNNaGNqRHdNbFnSAaMCQVVfeXFMTk5UTkdJMnFGZUVTaGYzOVlfb09aTFFwdVl2R0c3MlJIZ3NPd0k5czFyR1ZwVmNqWVRVcDdjTWNDaUNBbTlqZlFpcE1Jay01S2FzLURMV2RMeFhORXpWeUd5VUFYUGtNTW5YM0Z3eWtWZmVIR2loNU5NRXl1YWNNd1A0Q3lMNHcwNU5ndENaa3dwTnhjajJiMUcyUUdnb3ozWkEwWVFiU1hWcGZCVEZvd3VmRGRUSGhJT09WUTBsVTdmbjZQQWFWbGpXRENxcHVmYmJkZ2FBVXlCSHp0YWhlbm02U2J2anFUZHFoa29IeTZjMDAyalRRM2czYXJpRFhMajVfVkxFTlc3a29jdUdtekNQaGdUMWIxTU5lSWpMX2xpTU9R?oc=5</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1801,6 +2131,11 @@
           <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNUmVLVUFHYnVWdEV6UkpIZmYxRlVESm1pLVg4bmpEOVRsVUZOejY3SlpqRTdSNFNhX3lSRDZIRXNwbkd4R3NvcEh0cXBYLUdBdExMcU9PZVdqU2NVWW13SnpDUXNqMzRWdWNfMk9ETU9NRXdNdzBUcXdDU2F6cVN1UXJwSGtYNWZNWmRLR2VzZ2FWcGQtTi1kOUYtNlZHeVl6bERMcTIxdWh1U0VySmFQaFNPOTI2VWs2UzBUbFJodlZ2OWM5cEpqOXBocVRvNkdjbzNUSW1oTTlGODRvdS1XX0h1VVNlMmFYTDREWkZydUNXMEVUTlJFaGFCbmY5Mm9Ea2UwVGR6d3BPVlp5MkhVd9IBkAJBVV95cUxQM3lTcS1JX1dGWHFkNk5EcmdaODFmYVE4dHdnQXRqZlFOQm1VOTZlUm45WGFHN1BUUHdkcTI5NEp4QTllNnFJQ2FrRHZEOWJfRzhBZE14VG43T1o5NlY1T21BcGhfYmVRY3h6VzdaTE5IS1BCRHk3SnNlRE9mYW1FcURXcEFNOGVOb3dzaU1td0lJOU5FZzRTOXNlclhfeWdoM1NiTnBWRGl6blJ0emJjeGNvTjR5eFl6NUNlZkFxODNILUdHbmUtUEFkZldHcTlLSDk2VDBhMkw1eXZhZWFNVkF1b19fbF92akZWTW1uVUZIdjRPOGpsdVo3dk5WdXdmcFJKVVVhSXowRFlhR0xLRQ?oc=5</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1823,6 +2158,11 @@
           <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQS1dOcXVHYUZHVUFjN1p2eHdkRzBZNC1XSWN1NDVrLVFMOGhjOUdhdEgxNF9ZcGRuZUtKREoyZDJiRGpuZEtsdUVEejEyOTNDS1M3Ny1DdVY2VkQzVUpkVms3akFJcXRIdEl4a0RTb2VVcnI3WVBjLTQ4QzFOS1ZKaS1Nbk5rTWxoem5wekR1em53MEt5aHBvSjAxUjNlVFl1VldLNUNoUTRQaWIyT01JRlYteTJEX3hEX0RHLVk3b0hJVU9XeG9kbnJPOHE4U2dLNENkQnpwQ1lzRWlielZ4Qk8wYVXSAf8BQVVfeXFMTkdoN21tVWxSVG56ODNLclhqN0Y2SVpQZjFiMXpJT2lPZHRkd1N0OXhWeVRzRHFNMjZiZEg2UUNmUExyQ2tDM280ajJ0NEFnR2tRSC11VzV4My1aWU1VWW1KY3k2T3hrWUtjeXhTZHRhaDBGY3hiWGp2Nm9ZUmZHRTdjaVFMZ2t1Mjlra1M2RkFKdkhieVJPLXFYb0ZRLXV2Y0RxbFp3Q2s5Qk0wU1dEYThmQ25Fc0VPbmo1TWprRlY3WTRxZmt4ZkdEckVDdGVzSG5LUzZFWkFIOVJQZGp4LVYxU3h2M0oxNmhMSENKVTVoVDRkRDVtbzhVZE40UkVn?oc=5</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1845,6 +2185,11 @@
           <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPaDNXdm9iQWxxWXBaNDZMUldKdHhUa285Zk9PYU9mak55dG5EdWdxNXhzR2JvX293MjV6cFEzRjhrWW1ybWVXdUQyYnhGV3lJeTJGQUxlazJ5b20xVXMxckNOZnhkVks3VHVQYTB4SWVubGc4R242Qktld0FqeTdtUEZYR2Fod2NveWZ1WU9YMjBIWENTRHYtRy16b0hURFdrcGxwajdVR0VJWVE1bHdCalB6UkduU2lYdGR3?oc=5</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1867,6 +2212,11 @@
           <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNVHFmRm45dW14Y014NzF4X3FoMjRuT2cyelRQblQ0Vm95Q3BiWGotOXJsYm94Uzk1Q19hUkpxcm9XZUQwZ1E1eDBlTXp0WHh6ZWtfTDdjeW9YazdWbTJDa2tEUXk5M1pBSEZ0b2NMV0o4SXVLU2JIZmpNUjA1c3ZhSmY2dUZfR1ZXdUVvamJMUkNaYVhGSnZabmZOLVc?oc=5</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1889,6 +2239,11 @@
           <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOTVZ6ZjYwRWJ2M2pTLUFnWXp1MEc0eW9aN3AyNzNJOWtTcUh3Ynl4eFV0eEhUWkp2RklaS0VNYk5mbXQ3b2RISlJhcUpJa0Nxak1uaTRWQ3VHTUVwci11LXlGVExKZFlZc01YclZVMFBvOFo4UTBFVUdNTUVDS3NUbHRlMTZXZVhmRWdoNHUtVWNJNm1jdWt4Sjk5NnJMREJLaDJGbEJlN0JYQjBoeFFRMjFRTl96SFJ0cml0a0UzTm1hVUloUGhwazFwQ1ZMSU1HUm9oaXpUU3Job1lMZV9CWWVINzdSbmlIbjlB?oc=5</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1911,6 +2266,11 @@
           <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOSVBvNFREaG9FYWNQcjRhTFJ3RW50OHFrcVJPWHp6Q1g1X3FYZ1N4bW1mNGNfZDBDZnNEWDVjenNJbmlKQ09ORWxhekVxbHM4bmlTUHVPLWhEVWp4TWtIcThnNVlrc3RtNk5iWWhwTTR3c2VXdXBIS1JyTmZySUQ3cE5LVGFfOG1lV0tseXo5Q1ZGdkVTYnFUTVFDazI2MTVYN3dOTWNkTGpGSTQ1Ym5VMGkyVUdGUTNJZGl1VE4tNjJvYUMydl9QRFUzU1c2Z1RCUWhsQS1hWmZtZVVfRFNOVWlzdmcxNXlxM0hLUjQxTUvSAYsCQVVfeXFMTmR0ZE4yVXFFbEgyQ19XNU1TQTQtbjNCN2d1WmlqUE51emd6aEdoVjFPemlZZENxOGp1amVBcFhFamxscU1EVnZFZ2c0cl9zYm55akV1bmkzck9WeWd6RUpXbWFFNkZoUW1vTDZ5dUZta1FrRjFLaUt5NFpNYUFLVjJNU3RJZHZjU2c1UURqaG4xWmIxNXdsWklQYUNicVp1bFNIT1hnakVMa1VCOWFkWGVNeEVTME9JSjUtTmhGTVZtMEtqcThrZ2N4cjlEaE9VUll4TVY0bmU5UTZPU0c4blZFYUd6MHdlTFhBdHNlOVFlOGFJMXlncUEwcm12ZjdFamFIRUZtbVV6Sk9j?oc=5</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1933,6 +2293,11 @@
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQbFFFU0J1ekxrTWpxQ3o2dHpBUUlUUzdvUDZMR2J3a3BFa2hrVDZkRElIMVRkWk9XR0JwMG9pRXlVQ3hlY2RNLVhQa1RoRjFRbkFuVEJGaFZKa1lMRzJCenQ2SEFiOEh0bmV1NXVIOWI2al95Z3B1SVI4eUtiRlpseTlYUnByeGlOd0QyWXZrRnVkX1FsQzR0bHQ3UkE5cnBwQTJDWlMxWVU5QXpFZlg0Yk53cEhIdVljN3c?oc=5</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1955,6 +2320,11 @@
           <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPaDNXdm9iQWxxWXBaNDZMUldKdHhUa285Zk9PYU9mak55dG5EdWdxNXhzR2JvX293MjV6cFEzRjhrWW1ybWVXdUQyYnhGV3lJeTJGQUxlazJ5b20xVXMxckNOZnhkVks3VHVQYTB4SWVubGc4R242Qktld0FqeTdtUEZYR2Fod2NveWZ1WU9YMjBIWENTRHYtRy16b0hURFdrcGxwajdVR0VJWVE1bHdCalB6UkduU2lYdGR30gHAAUFVX3lxTFBvLWdkV1R3TDA0Q3NuUU1fVms2Y0c5SzgzM0tUX2kwZkE1TU1ENTB3TnRyU2ROSlVzcnBZeFdvU210emMxNlYxMFFPc1dFdGdVU2dNNWViWVRXTE1tQ2dBVkpmOXBobXBuQzhhWU5rSU44bG9wWV9MV2dpYVItUDhRZ2x1U3FzeW9tODRkQVpYN1BQRUtmeWF4UWpFbDlDLXBJV0kydTJsRE4tdDR4UHczcDNJWHBGVElYaTBOVHJfVA?oc=5</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1977,6 +2347,11 @@
           <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNR3V3anFMQVktXzNpOFhrU1lTZ0o2MEptV1RtdXVmTFZKd3F4dFpUS0ZYYjNrbFN5V1RHSk42bWZUZy0wLTVkN25FT21RNGF1eFVZQTNPcU9id2drXzZxY09ubWdIRm90U05FXzF6aGxLcUpSOEFqQ3dhdWZWZDRtdXd0OFBJQmxIN2d2bG5PMy1fay1vRVEzVDNUelJmSWhnWjZoUHRkSXc3WjF0Wk54SktRWmo1R0dZSEQwVkxrMm1IbnBkcEVkU3UwaFlkR3BRSkN0MkNMc0pFNnVBUFBoUjlFQXBHazlVM2pZWGhmaXZuVlg5VXhF0gGEAkFVX3lxTFAxR2xXZWZ1RHVOU2ZSMWdrcTNpeUs1NmVrWjRaa21sVGtkNFpJLS1aTFRnbnRmM0lfNk5TRTNyWXNPSWFuM2hVMW9vNjdndkxKRTMxNVltaDFEUUF1M1VDWVd3NUVPNGFpVHh4alg0ZHMxQ20zb3dIVjJPUXlVRmNMb2t5RFl4V1VsRkhmLTVNWG53Ml96NU1mdVlEa0NiX01PM21wVWZvYThEQ0tkYnJ5TldfQjZSaE1nMUJvdHV2NTZ2c2M4d0xZOUJTQ0pDZEw3TmpyRDkzWHcyVnJHcjVNcnZRLVdNRWcxaGRiMm40SWdkRXRzNm1ucWtJbWtVYXpQTThM?oc=5</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1999,6 +2374,11 @@
           <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZDlMS29BbjFJUnZwaUFkb0hfR2VQbzVDVG9XdWVfYUZrU241dDFuenpTM3dDTjRNMFl5UG5tUWNRYmFoSE5xYjB2VG9zYl8wT1pTN0RmRXFlOXpub1NlSkpwRjhWR0pidlhEd2dTR2JGcGYxSkVtaTFIb3poUjNOSnk3Rm1sQUlXajdjZjM5NzhLbDhWMFJSQVJxTEJwZm9zVFk4bFJvUkw1Z09OU1ZJT0RVenZ5cjRVbVd6TlhTd25leUpQN0ZQLXVmdWprcEYxeWh3VlpZMDRZcG5j?oc=5</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2021,6 +2401,11 @@
           <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPUVlDTjFRSFIxbERfSWlvR3NwWWp5ZnVfWkcwVmY4UWJwN1ZHRE5hZEt4bzk2dG1IeXdBd3pydFN0LVZDd1U4cjlCZTY1c2pXR1h6cURfSGFQU2RQWS1UQ2ZNQWpna2ExdWVEYmpFQlp6d2hBMGZRWGFOUThlVkk0ZDZXWTRneEsyLU90TkxySk5sZ2UtYlhkRUxNNjNDY0tVWUVTdWFUT2FIMGNZNTVjWVBwRXoxcHp5eHM3dFVRRkFYODBEZ3RIMlNyTzZVV3dvNG9FSTEzRGJ5eVIwWjd5d0VaaXpkNTJkc2Jj?oc=5</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2043,6 +2428,11 @@
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQYk5jU2xzQjF6aHl1bVloUnV2Z2FHTE85aVcteTZOWlNlZk1NblhURGlqMFFIc2kwZmtuNHF5Q2RZb3BKaXlZUGYxZHFRbzBFQVA2R2ItRDVzMjQ3d3l1Z010SHNRaXh3YUlsWHRzS3A3d0xneWJJcjRsWnVNSzFjT1FUdGl5cVVfY3dNTTNsZ3AtTDJRM0Z1cnpXREdnY0JwYmNiZEJBcmltTW51QUtMSGtabkdFd9IBuwFBVV95cUxQRjB0dXg3YzZnX1JuUmFNLUR0ZDNMN0dUc3ktdG1mTkxVSDFYU3VGS3JQMEdLejMxVnhXTDFyY2pvZDBQYXJSUVVIclNSV29LckVJdWtjczJsc01hM0llSlZmandRd1VhRXlGSnFzR2Vwel9WbDNaRDVKLVhKd2JZUkhRVzhENHlfUTRsS09SUk95SWo1ZGNWRFJBMDE2bXF4N3VGVThRZURtQ1UzUkI3VnRxd2hNaXgxcklR?oc=5</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2065,6 +2455,11 @@
           <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9JcWFWZzVBMnZHNk1LWGlrZU0xSERod3lLNHRYWENlcFUwTWJpLXpXVEo2TTFhV0tjdFpJd3dwYU9hQ09yemF6UnBWbnUzVUQ0dnNCVk5SQlNoVFBySzhTYWNLMXU0NDY3UlFUTFgzU0tMcFU?oc=5</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2087,6 +2482,11 @@
           <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOaHlPaG16UmgtQWhON1lNcFowdVNnTE1DQlktVFNqRUUxNkZ5RVFZQ3AyTGdSak5JbWxuUDdmRGFPLVlnYVFPNzI2SUdlMWswS2cyeW5IVHUxdjdMTzFWMW93VlFxLVRFVGdUYUN6YXJldngtS1dQYnVmcDl0RjU4Tmd5UmkwSG93NWU1anVmREFKNUp4S2c?oc=5</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2109,6 +2509,11 @@
           <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdnRLdGVRRzhQXzA5QUlOTFZOQjB2QTRWS25NakVkZGJ5VEVpTmRsQlcxZldZNXdQaWRzeUxzQm43QTdQbWp5c2RqcDZEaHRPazlhbXZxWjh5b1ZkYWhSVkFZZFBPR3M0YmNCeGgxcmEzd3hUa1FlN0k0UDFSbFM5WEU5NVdoc19UWW5iU3lfXzVudXFGSHVYVEpHOXZYdFV0X1NPM2FIRWlQUWNPX3pXcF9hU3FtVGd3YTFpbXkzbEhuQWppVHc?oc=5</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2131,6 +2536,11 @@
           <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxORkJOYXdjc05xSzk5YnFFdHdMNVJvSmsza0hURkpEemxBUG5fcmNrQ0VoUVVUU0V4MnVuNHNBdFJ6NGg4Mi1jMVlkaVNtaGI1dVlfMXQxUGVWUDNreGtLV0VnY3VzRDZZUEVFYlR3amVCQmdMMUkxZXptMklVb3R0b01Ydw?oc=5</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2153,6 +2563,11 @@
           <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQVklrUDZFZHl5NWQ1a05qUUVkRHpnMzNzTHkxOG1RZzg3aTNoV2Y1Qm5qOHZfY0RwZlNVcEptNzNkYU9leEFVTURaMDZDU2lwc2FuODhNa2xtRW5hTXl5dG9zZFhKMHI3R1dMQnRSX3JzdTVVWGtERzhqR0ZmSkp1R1l6cU1fcl9yZTJzVXppMEJMbmZVRlZLZEkzYlFWOC0wS1R4MGNtQ0NjOFNlcmhv?oc=5</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2175,6 +2590,11 @@
           <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOMmNVMHc4M3B5RzdGRW1kNW56aWRTVEQ0b1c4OUh0aTlsVzU4S0h1elA1WHI3b2hsbUJiYjY2Y0lqSUQzXzFzX3Q1NGc2NU5lQTlTNVJyLUhURC1jLUhOV0J1RDBGbHpYSHZQT3VJSlByRW84eVJnenVPOEpjUXMweC1KNmU1RGVsQVlWZDF0VXZDeGJkR1BXTHc0Y1l4bVIzZVpyMl9FcjQ1SFRq0gHHAUFVX3lxTE5GLUxXYkhaamtBSWt6bnVlb2FlVnFjT3l3ZDE1bVg2Nl9teHhfbHZsVGZFZXZUeVZKT1BqWk1CRXZJX09rRjVjRnhLWDVuMTdHRGNkaEJtcGJ6UkRUdGVrSW9JSHBtTFQyb2tPU2pjN214TVJxOU1IZDJWMUtUaF9BcUJ1a1VTdGsyTGtkXzVOWkg0S0ZMUUxVTE0xU1k3dG1TSHlnaVJlXzlaV2dUc0kxQUtyOEZwQ1J3M3dsV09pdllIeHZpY3c?oc=5</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2197,6 +2617,11 @@
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPR29qWGU1TEdDRm9TY2lvZk9fOC16WTdOMHd6QWZldlVsTUkwYmc3S2NRWGRKVXBVckJUZFJLNzR6UXpBZjBVSXVqUkJCeGNQZGpQMmhHT3VnNGN5cVBLcDUzUUd3cU9OajZxNDMyRE52ekxrclFtbk01Q09wTDRSdUxPOEc2bWN6UG9lUmtFUFpja3lUV1M3UUpHVEZNR25YbDVBTzdTU0REZkwzM1JBYl9Cb3RaS0hGS0HSAc4BQVVfeXFMTW11OHlyX0Uxd01rSXBNUUxwelpNWnRFY3NEOF9tR0F5eTRPMFJ2UkFaRy1XWmpPLVFKUGhkSENxbkdTTHpxOHpyVW80SGJBZ19YQnZ6dENyR0ozNWZRcE54dFdSTVhqaWRWTWpsZ2YtbWRMRGh0dEJ1d3lVdDFXd25aMjFZSUdvYnlmekV1ZEdYWUo5TXpZRnp3eGJtVDNja1FacWt6NmpGWmlyb21DTTA1ZlBvczJGV2s1cm51bVUxblRoZ1kwaXl3ZWtUYkE?oc=5</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2219,6 +2644,11 @@
           <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1YZVlMSEdJTEVjT3IwY0diX3NlYkppOUI5cHlQd1VSd09hLVk1djltVURIdGEweklZUFU5X0p3QnpQMTM4RVVTSlZic3B1Y0R0MWlPNzFlOXpia2xqUXphcVJKdVhmQ0tZWUtoXzBoc0cyVTkwN2Mzd2dCcmdrVjg?oc=5</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2241,6 +2671,11 @@
           <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQblotVFlYS2gxelhzbWswbnlHMllZRXR4Yno0OUltelNiampqNk50YjNpM0JVVzNVLUJfSkJWbmpGQ2pMMXdHYTFfUUNJa1NSZ0FBNmpYSkFhbGFlajFfd21EZTg3b2I0cHpYX1BBMmQwbUFGRmlHRnBNYTZkRDFNblhJRGkwRHZFOE51cWt6SWpwM19kRHo1Q2QzTEROQ21TaTN1SWwwUHROR1pxbVBLRVhOV2JyWWFvcEpR0gG7AUFVX3lxTE9fQV9WWGtVODNQMjI2b1NEdXR6TDhjaEFxeEY1ckt4Qk5BR3VsWWJfMFF0eEdtU1RHNEtIX3M1d1JyV0hBRFpRMVBuUWxUV09fUDYzZ3gyRW11YVlqMXZmVC03cWpwRlkwLWE1dzNoamttVGhSaGNHMTY1dWFUYUM4LW5hNF9YYnd2WmNUOEptUjNLUjdvMDNkVjBVWFdDLW9yVzBHc29ZWUdzWlQ0TWktTE9QZm8yaXNnWlk?oc=5</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2263,6 +2698,11 @@
           <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZDZleUJVQUxpMEFGcmhUTzZ0WGtiUVAySmhvS0xIdjJ3cVFvUlFHNEtUMkFPRkIxQjhydkJoZDlwdXFWbkwwQlNvZ25vTzZ4MUNOOFZJZXZjbHkwZzZ5THZLQWxOV0Q1empqcVZuVG5EVXVtY29kOGltYkxER2xVc1poYTNUcEFkSW9rNzZkV3BJUVF4T2dMb3RIS2xjaXVCTWZJVnJQd2Y5UEpMMWFocFRINkp6ZW_SAbwBQVVfeXFMTU1RaFlFRkJCZk82cmVXR3NLelhiaGhFRDJhaWpTR1RzamFSQnFDcU9aaWxzclhyNjMzLXVMZTA0SXg2YWtoN0RvM00wUWZ2Vmc2Q2t2RXdYS3BZaHFJRlNVYlpvTF9QS2dlZzhwSUJ2VjJRTmo3c0FZX0R1dlpmTy1mVjloNk52LVFILUwtb0pjVFY5dEJMMzE4X0ExMTBSZTVNVlZhWlh6eFFsZVE2RVVoaTZmaWo4TWQxY2E?oc=5</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2283,6 +2723,293 @@
       <c r="D85" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNdUhGNHloeWdmUXVSTUFneXAwbkJNN1g3TVgzUnU1aEtiUHpqUEo2UW5CeTFyWEQyQjlMWWZtQ0lhWkU0emxTdG94Rk42YWhCWEFIOEhVaDF3SUNNa1FsYXlERmxCQ0tuRUFidWJkN3doN1Y2WnVfSzBsWDlndU9nSXJYbVFqTzJuQTJBT3N3?oc=5</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:59</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>La agonía de viajar por Colombia en tiempos de la fracasada Paz Total - Las2orillas</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQTTVPTkpYTEN3VXEtLS1leHFBeFJqSU5xOG45TXJaVEliTy1nZ1FWTDc3MXh1eWllVXRCZ3JJbWVLUjl4UmZrMzZaQUZVYkp6NWZYLW1SN1dGemR3MjMtSWNDYU4zbE5vUmd0U2NsU25UTF91SzhUYzRHbUpHMFMyOEVvajUyRG1HSGJDeHRtcF9UWDE5dng1NWtCbjhKQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>La agonía de viajar por Colombia en tiempos de la fracasada Paz...</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:59</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>La violencia en Colombia en el marco del posacuerdo la Paz Total (2016-2024) - Dialnet</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9pNHFhMGFxYUNGcW5NMTF5aHJ6NFpYaVFCcEFTSEtFVER3Tk96Uy1pRGVLSEJxWlRTTE80QlA4M20zVG5iSGlaeXpvYzNQU1BqcHFqUW8tWktMN2M5N3RzejhIdkRVckpYMGhLSA?oc=5</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Acuerdos</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>La violencia en Colombia en el marco del posacuerdo la Paz Total...</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:59</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>GameChangers 2025: El laberinto sin salida de la Paz Total en Colombia - InSight Crime</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNclNUR3NTY2FQSjdqS2RZbk5FSlB6cHhsNm8teWkxX040VURyYXN5NXA3aVlhTWN0c0tEdEgzLXNveHluWUJsVUs1eVM1SkwtVlVWV0k0a1F3ZS1OdkZaZUlFS0RlekpjbExxOGI0SUlRc1VSQWtXRHdPTXR3a1VRanFnRkVicEVZNV9JVXRB?oc=5</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>GameChangers 2025: El laberinto sin salida de la Paz Total en Colombia...</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:59</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>“Uribe desmovilizó, Santos también; paz total de Petro ni a un criminal”: Claudia López - Blu Radio</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQaS1yWlluWUdzY0VqRDBXOEdxRF9ENzFqRzl3aUsyN0VWZWR6T1dhTkxtLWJXMEdWTVR4eGh2SVVhWi1ReTBOcjNOeUhkY3haWlpoa2dnZmRRRGlnSnFuVGlzNVRUaUtwOWk0a3pkSHJCRWhOdUdXZTRlTTZfVlI5cW8xNVIyVkNwMVFQem4xcnhPamlFTWdmdnlXeVFLQnVscFNpd0Z6VE4zZHhfUE5LRzFqaVA3WUpKX1hEaEE3TTZlbkVWV2RtRmVB0gHXAUFVX3lxTE84d0R1dDhtd0gwTVM3Qzhfdm1XMGtpUzV2aUZrTV9NMGhKTnBNNWpSbHl4bGx4UU5mbUxBMl9VZndham9RejN5LXhsMWJSMXJ1eDFudm9aYUZuTHV3TThfbzh4OTVzMmxHMk9rZF9Kdk93cjctaGRLU2lHQ2hhZTR4VHQ4ZXpWenZEVXBnWGNUZjQyR0w4eVpWMTcycWlEX1lLblV0QWlkWlZjSnlZcnZiQ2I0TE9DYk1uQTFnb2VzOVEzMlZXY0VhX0FJdG5RM2NjTmpVLUlF?oc=5</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>“Uribe desmovilizó, Santos también; paz total de Petro ni a un criminal”:...</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:59</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Cinco Continentes - El fracaso de la paz total de Petro - RTVE.es</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOenVlN2pOSTFHVGl6RV9weG9YRF8yQ2puSDFPek9kQ0RvcTZRN1JyRFVJek82LTJIajUtZFBONFNsQlE1X042bHJQeTR1VExfWnlDZnFKM2FkOWFmSzBJZ3ZSUGFkU3JodHJCVFltWm1RT0Y4NmxuUG1pa3dWOFNoWVNYZUd2TE5BWGxBOVJTSXR4bW1vZlA1M0pjbmhuekJXdHY4?oc=5</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Cinco Continentes - El fracaso de la paz total de Petro -...</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-05 14:59</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Las críticas de alcaldes y la fiscal a la paz total de Petro suben la presión contra Iván Cepeda - EL PAÍS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQdUFLRmZSdVAxTVdhYWxCUFpSZ29mT2xtdVZJOEx6N1Y0bmwyTGcwbGd0MTFNa0dlMGQwaHhpNG9aZjV3NngwS2pCSTdzbmJIZ2cyMVVYZEJPeHNwYnJQbzFySjBiZU5PZExZSi1tWnZUVmZKaThGMGg5U1RURW90S0E4Skc5dV9ULUtaTTJuOHRIYWZZTk44YXpwUDZBbWQyUWk1UDR0WkREbFkyNHF1eWJ1TEJTSHBLVzYxZE0zcGNJSVRDZFYteFNQYVFGTE1LOWRCVmJJWG1CempnM3d3bEtR0gH2AUFVX3lxTE5YVGdnR0VvUGQzdUF2RGxncHcyS3MyaWNfcWpCckpuWW9LQ3hKYm02dkpKNVdjUDBiSjBTNEdDVktoNjh5Y1NqWk9nU0NVUnVaSkwyVHlkTHF4SlQzMzFUZzdEcWR5UVRyS2VLSlhzSmFOTkpKMlVLMEJaMWpwOVN2YldpdGIxMV9ZVnR5eHNBaElzNnluR0hSZWVRbnVjRlZGMVJGeW04cDljeDU4eTROSENCenJSR2FOU3NrYWtQVmVXNUtmd1kxZ20ybVFrUlpqWUYxbEZKVXZaOG9Qc1BfZjJZbzhGcGN5Rm9JSUVuRXVEaGFlUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Las críticas de alcaldes y la fiscal a la paz total de...</t>
         </is>
       </c>
     </row>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3013,6 +3013,100 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-05 23:49</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Gobierno Petro frenó la captura de más de 200 criminales: 81 siguen con beneficios de la “paz total” | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPNS1XemVBaTR2bml2anVRSUxrTENaY0xiVDJqQzM5UzVReHRRLTVjbW5vZWRBSGVvSlVybkctZEhFZU52RUVCWmxleHc4Wk9ycGhfb0JSeFU3alJNa1NSVjVjNUNhQWhYbURWUEtvclFfNjNCZ1N0Umh2ckdIY3ctTkhJYXI5N2s4M2d3dGdkZkxCY0RIQktDN1pidHRUNmV0Z1dqN3hKWkNoVjTSAbABQVVfeXFMUG1aU0lLdkdSMW96WkJna3dTTkZTbzEtZjNWNUxRSjZ0VlVFRkhpNlJMcEdWSEhubjNEU1p2ZFVmdjM4UmJnRml2SHNzN0lWSjFBWmQtalZveWxuN3Jad1JZSXltV3lkM2Z4Zzg1S3VScFFWUk5hSlhETVZNc2VHMHpTdGlnQ0FPbGZKU1FjakVxTGdja1FiZUhCeEc2LVh6alBmMEZlZHNkdEttYkFYSkw?oc=5</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Gobierno Petro frenó la captura de más de 200 criminales: 81 siguen...</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-05 23:49</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>¿Está fracasando la paz total? Así está el panorama de seguridad en Colombia al cierre de 2025 - bluradio.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPd0g0Wk1qWWJhbXVqekhmQm9GTTRFa3k5OHMyM1JBLXctODZQV0d3aEpvV0RFWFZWN2ttTm5IdmhpWjVXTjlpVVk3a2xCY3YxUkpzUEFvQWMzbXlnOXJLZTQtY0ZrNFExMjJnZm9ELThBQW1hUjdwMEpiTEppZlhZeGM4M1pMYU1YSEVwV3dpcW0xVklwR2pfeTBfUWE4Z3JidlBKejJwVUZKYmxTNC1IaUpFUUdCUzluWk13dnV0SkV2dDZQR2NMTmJ4bkl6UdIB2wFBVV95cUxPUkhLRUhOb2JobDlWMWF0Nk80MWFOVi11V0g2ZmVZRDhFVDVvcHUxbE1ETUZJaGhRQmViZEM3QmVQUDJqY0ZTT2ZzOGY3REhXT2FQdTNvaUtjd1B2RXEwLW9NcTJnR1ZESG8tQmVsVVFQUkMxSHlfUGtVLUwxOGtYVDNHeHhtY0ZvMU9qcENqUENtVDJXLTZZOW1uVVVERV9BcmM0WF9EUkFvQ2doelU1UzF5NGg3YWhSNlhBcHM4OFdFMnF1OHRKeF9RVnc3ejB6bW9EMmUydFVJTW8?oc=5</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>¿Está fracasando la paz total? Así está el panorama de seguridad en...</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>Resumen</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Tipologia</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Territorio</t>
         </is>
       </c>
     </row>
@@ -489,6 +499,8 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,6 +528,8 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,6 +557,8 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,6 +586,8 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -597,6 +615,8 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -624,6 +644,8 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -651,6 +673,8 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -678,6 +702,8 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -705,6 +731,8 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -732,6 +760,8 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -759,6 +789,8 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -786,6 +818,8 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -813,6 +847,8 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -840,6 +876,8 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,6 +905,8 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -894,6 +934,8 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -921,6 +963,8 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -948,6 +992,8 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -975,6 +1021,8 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1002,6 +1050,8 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1029,6 +1079,8 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1056,6 +1108,8 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1083,6 +1137,8 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1110,6 +1166,8 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1137,6 +1195,8 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1164,6 +1224,8 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1191,6 +1253,8 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1218,6 +1282,8 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1245,6 +1311,8 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1272,6 +1340,8 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1299,6 +1369,8 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1326,6 +1398,8 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1353,6 +1427,8 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1380,6 +1456,8 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1407,6 +1485,8 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1434,6 +1514,8 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1461,6 +1543,8 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1488,6 +1572,8 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1515,6 +1601,8 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1542,6 +1630,8 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1569,6 +1659,8 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1596,6 +1688,8 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1623,6 +1717,8 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1650,6 +1746,8 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1677,6 +1775,8 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1704,6 +1804,8 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1731,6 +1833,8 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1758,6 +1862,8 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1785,6 +1891,8 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1812,6 +1920,8 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1839,6 +1949,8 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1866,6 +1978,8 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1893,6 +2007,8 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1920,6 +2036,8 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1947,6 +2065,8 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1974,6 +2094,8 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2001,6 +2123,8 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2028,6 +2152,8 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2055,6 +2181,8 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2082,6 +2210,8 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2109,6 +2239,8 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2136,6 +2268,8 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2163,6 +2297,8 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2190,6 +2326,8 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2217,6 +2355,8 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2244,6 +2384,8 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2271,6 +2413,8 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2298,6 +2442,8 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2325,6 +2471,8 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2352,6 +2500,8 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2379,6 +2529,8 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2406,6 +2558,8 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2433,6 +2587,8 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2460,6 +2616,8 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2487,6 +2645,8 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2514,6 +2674,8 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2541,6 +2703,8 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2568,6 +2732,8 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2595,6 +2761,8 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2622,6 +2790,8 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2649,6 +2819,8 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2676,6 +2848,8 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2703,6 +2877,8 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2730,6 +2906,8 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2777,6 +2955,8 @@
           <t>La agonía de viajar por Colombia en tiempos de la fracasada Paz...</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2824,6 +3004,8 @@
           <t>La violencia en Colombia en el marco del posacuerdo la Paz Total...</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2871,6 +3053,8 @@
           <t>GameChangers 2025: El laberinto sin salida de la Paz Total en Colombia...</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2918,6 +3102,8 @@
           <t>“Uribe desmovilizó, Santos también; paz total de Petro ni a un criminal”:...</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2965,6 +3151,8 @@
           <t>Cinco Continentes - El fracaso de la paz total de Petro -...</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3012,6 +3200,8 @@
           <t>Las críticas de alcaldes y la fiscal a la paz total de...</t>
         </is>
       </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3059,6 +3249,8 @@
           <t>Gobierno Petro frenó la captura de más de 200 criminales: 81 siguen...</t>
         </is>
       </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3104,6 +3296,65 @@
       <c r="I93" t="inlineStr">
         <is>
           <t>¿Está fracasando la paz total? Así está el panorama de seguridad en...</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:31</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Paloma Valencia respondió al ELN tras su anuncio de “juicios revolucionarios” y lanzó pullas a Iván Cepeda: “¿Qué dice el papá de La Paz Total?” - Infobae</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxOblcwbndLbXFSNWU1RHBRZ2VvYktIZEhXem5kWmlFZkF3U2ctQjBmT1hOTVA1Wkp0aXFhQW02UXoyTWtUUHlBeldkZWE0d0I2VGZJdUxHekdEZURob1UyR2xZdG5xN2s1WF9iM3FFUFVNSnZmWXJRWDBRYm1rMGNjVVlDME8xTmdXWVdHc1BBQ1NyeGdaNjRXTVhpaDR5YVZXUjh6aXdLZDAzMWhWWGhXN0dTNU85UGU1TlprUjdCYkVHS3FKV1FBc2RKeGh3SDJsMnJZajFrMnoxSW9CVGNHNk1WZ0Fra1NGY0tpQ05aM0JpN1lZc0x3SkVGMkZhckszckQ5d2hlYXE4WTg5S2ow0gGqAkFVX3lxTE9RR2Y2RzFkS3EtWXNzQ3pDZ2gzR2pmdlJHN2dmcFlJU2ctN0FRdlgwdmlKTHJhVWJnRW9OVV8wNlpHNVR6UEhYMHFwN0NiOTU5cTR6cUhTSFFVajdkYzkybmIzVzhxNlh0eF81b3lTeGhxWkxCNjg4SUdqZTFldllDaE5DQ3hJdzlMRUpvX2h6eF9ITnJiVnkzc1FFTnVFNWJva29oNGJvVVBXVzlmbE96a1lKUlUycEhFcksxZDI1NkJvSFY4UC16OXJ2a09YT1ZSTjBPSmhHbmZBRDQzOWQzNEw5RVdNakRvVUNBb1RQM201X09tOG5pMXBJVVphYVZJY2lmVHROY05QaVZ5TTNUWUI5djBPLVdXS2JnNnNnWDU0LVFsTW5rRlE?oc=5</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Paloma Valencia respondió al ELN tras su anuncio de “juicios revolucionarios” y...</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
     </row>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3358,6 +3358,63 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-07 23:54</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Paloma Valencia cuestionó la Paz Total del Gobierno Petro tras el asesinato del periodista Mateo Pérez y señaló a disidencias de alias Calarcá - Infobae</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxON3pKSXdIMU1nbzA5NXJKaFg0NzN6eHl5eHB0aDlSbmFoTnlhUGlfU3ZDdEtmR1VocU5kbTd4SDBoQ0lqNGRlcmZMWkt0Mk1ISzR3d3RranMtbGRXSFY2d3U5dHpVaTZVOVRWb2VyMTlFdGdKaTduRHJSVG1PZTJZeFZsbGdSUC0teURXTzBqbzNuUWRMazVDSE1QT2xtb3EwOXV6eGlabFljY0JiSjdYUlRyVjk1TnVfMmVQNno2dFlLUjhjblpFOXVHTTNqUF81eDBRaXYycXdXampiZ1lQUVQxV0MwRk45eXlWNzdlNEJDV29tYTRicUMxUl9zMHQ3bktVaS13emZYRHdZWFF5cnIzcU9JZ9IBsAJBVV95cUxPdVJpUGk2YTR5QzhhN1dIYzZoZTRuN2l2eGswRjdjRzJRRXQ5ekxlNkQwUG42NGdhT1FGZFc1bUs2ZGpIS01HWmtXaC1qbjREdEtQMEFjdWIxeUh1RHRfUFNmN0xMWEtoWlpZVExKQ01QclhqR3VGMFBLQU1GdTZTdldoT1JZZEF5UXcyUmdmZEhxaElTTFdQOHZXWDFDU01FUFk5d3gxbGlnNnNtZ0RCZUl1ckZjUXpHcXl0eU9FYTdiV1lKeGUyQ083N3pHTnRUY3VwbGZaSVRhWm1LaldiNG9tbWFIOGJzQVl3SEc0bS1tU043OE11dFZ5bUU5SmRpWEVkeVQ3Mnl6clQ0VUM1LWVTTmdvcGJnQjF3R184b3VfYU9JNkpoXy13aFdYOHZ1?oc=5</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>EMC / Disidencias</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Disidencias</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Paloma Valencia cuestionó la Paz Total del Gobierno Petro tras el asesinato...</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3415,6 +3415,120 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-08 14:05</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>El 7 de agosto se acaba la ‘paz total’: Paloma, Claudia y Fajardo coinciden en que los diálogos de Petro con criminales son un fracaso | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxOSV92V0J4Qzd0cGx3YUVRVmVvNmE4UHVncnAzUXo0RzNmLVUyZVEwTURCQWNBNUZ5LTJRZ240dk5mdk5raV9xT2tiMmdIeFRHRXBSamZ6a3FRc29vZFpSM3drZVBwTWpGRG44UnFKQU1XUkhGcno2dHhNRGVhdkxDU0xseUVmdXRWb3l1d3BQZUpyQm44RHc4NzBaeVVOdWRTMVhySkZfeGhkUVp6cGQwaTRiNmhlSjVYS1ZsZHVFdVI1N0VIT2tiRkRtY2gzMnI1WEFxc0tYNjN0TWpGc29oYXBTbTk1b1RGZVhNNFM5MDZOcXVnb0hsdDByUndINHRtRjFxN3h4ekR5SHPSAZACQVVfeXFMT1lSZkpnNDNqMzBhWGZEa2cwdmQ0VXkwQ0MwNnRIV29PUlJDbzllUk9SdGQyNGd6em9mX056Mk0tcDdmVm5ZVk5pUFJ3V2JZbG9LckRyeHVRVTZUTU1vaWtFTDFWeHNEU2FMT1lpQlNfRVJ0d0pyMTA1YzNXN1hENm5FZHdJdzFnSlM5WXVoMWlqdkVBQkc4R2s0YmI1UjN0cVk2NEp0aEdDM2JFVlg1T0RzSG1MeVZMb2xMc1p5YnBhWVBmcTUzWW9Pci0zVzdVYWdIZUJNRXZ6dTVkVnA3WkxrUUtZZ0xWWjE3bHZ2NktMbWlnN0taanZQcEE4Q1l1RkVMQW5EZW9PTXpCTDJ2TmU?oc=5</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>El 7 de agosto se acaba la ‘paz total’: Paloma, Claudia y...</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-08 14:05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>En vivo: El 7 de agosto se acaba la ‘paz total’: Paloma, Claudia y Fajardo coinciden en que los diálogos de Petro con criminales fracasaron - MSN</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxQb2FRWXJQR05kYnEwUFd6cDZyT1hub2p3MzFORkJHem5HbWJPZ2hsRThPTW10Mkg2YWFNQUtrSm1SLXNFaWRoX2xaVnd3UGtJYktIcy1DZzFkTkNYOV9BTGlrd25JZk5DT0pTQ2hyVHBvZkttX3RwemhORnZHcVJQQTFITWwtaUF3ZnUyN0hpb1VrMFh4SmdlU2JXMmw3QTJIcHRGT2dHWHdPYWVaU0xWWlJfX0RkME5oUWl6Q0YxeDhSXzJaVEZvTWJlaHRKSVlWeXc0b3JIczFWVkNFVi1hZV9FZnJNWmtsYXYzMnpnbTc2RUdaLWx6M1dKNzFZSTBqQV9rOHY1RFkyejZZWWVDZzBSMkZVMXNjQVlLSg?oc=5</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>En vivo: El 7 de agosto se acaba la ‘paz total’: Paloma,...</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3529,6 +3529,63 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:40</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Académico</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>eln y la paz total en colombia: las dificultades de un proceso de negociación que nunca acaba - Dialnet</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9ZQTRDNXdGdGZraTlZdVhpOWpMcllZR2RHbHBOdWtOQzNmNjRSY0s5WVkzNUZKMkF4WDRzVUo0Zkk1ejZ4VG9JajVqU1dnRExKdHc5ckhCWTc4Sk05ZTlUdFMyWmp4U2J5?oc=5</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>eln y la paz total en colombia: las dificultades de un proceso...</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Paper académico</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3586,6 +3586,63 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:27</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Expresidente Gaviria rechaza suspensión de órdenes de captura de miembros del Clan del Golfo: ‘convirtió la llamada Paz Total en una rendición total' - ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxOQ3NQQ0ZmdTRBb2d0S3E5RnRrZjlyVTczekdfUHJsUFdFZnJSN3h3RE1wQk9xUngzOWcxXzQwdVpiZjhqdE5BTlpxcUFzblA3OXpsMXV1ZjM1TjlRNnllWl9TNHNFYW9meG9ySnhFM3l1ekpsX3Awa014Z19XU0g4TUtBUFhHRUpteFNKUzRmSXJLRWVTMnFjbGh5NFN5dExiWkpsQnJYR0phVjBuN3pSSVFEbnNQTjhJSUxuWlZPQzdmS2RUMmZLUGdBcTZpVmZra2Y0SmNGLW9xTkRqQ0lhS2NkcV9NWlNuakxMU2dWdThOS3ZnWGJOYzEwN2drbGRCVXdvaVNXa3E1LXA5aWY1Ukl0eThGWkx6U3FRc2NET1FKN1XSAagCQVVfeXFMT0ZSQ0JNRVBMM2JLMG05MGd4WVpYQWRtUFA1QXozTHQ1cXFHN3hyUndTVHkyMjIxS3NEa1BWUEg1QlFfWEFobHQ5NGRWWjQwYTJxallCMzNlUzBUWnVoZGRuX2ZHV2JtYWZ0eGpBUXhla2ZYam4yOWVxWTBlNXlZR2ozT3lEYWtkcnppcWwyV1ZmeXVkNllGVHV1aXdGMnY2T2g2QkRRMGZXVEp2dVF5bDNLdWdmNUJnX0hyTW5kVWJ3X19LMWxhR0VFUURFRjdEZXg0RVBYdVQwdzl3bWJtSG83RU5TQlBnU2FuY2I1X25mTjE1cW0xeGVVejgtcjNUNVlfVzJMOW4zMTlqVHFzTTVEd3JUYll3dHlKVkEyZHJ5UWVtVUU2Y2M?oc=5</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Expresidente Gaviria rechaza suspensión de órdenes de captura de miembros del Clan...</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3643,6 +3643,63 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-11 23:59</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Gobierno Petro destinó $88.840 millones a diálogos con grupos armados: denuncian alto gasto en “Paz Total” sin mejoras en seguridad - Infobae</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxQa3E3enpabDhKQ0ZNQk5laG5yTHlXVkMxUzdWLXltbzNRLVl1YVRtQ2ZOdmN2MEhlNGJMZUZSdHQyVmhlUTlqUDFfSDhwSDFiRncxOFpDTE5oN0dJTkZsZ0RWMjF3M3hzSlBNZ0tqYXJueFpKVXdiY0xzNUFPbklXMXB6MzBMTGVGbUdzNDN2Yk1zeTh6YWlvMGxoVjhUZnM4SlZmNWp2cGlUSVRaLW1mbXM2eWFhR2NwdE81UHFEOTNKYnlXQXFBeThOenl3Z1BMQ3pCVnpHN3BPZl9CWWRiQ2UtTHVYZjh1ZFlsb19RTC1ZRmUyQy1aQXZlckpjdTZx0gGbAkFVX3lxTE9feEd1eVhlb2dZQkdnbW52SnRKLTJEV3JXNVhiX0k0eF85TWRscFh1VVlfWUlzbWpRVk1vYy1NSmRDWkxSSjZub1ZwMmVyQmlCVHFuN2xhbXRDZkRXaHNMNFd5WlpxMzZ4QkRQZUdSc0pZdEphaGJsTlgxY0lDY2JiMDNqU3huSGZJQ0hjenJFOHdqSFdza0thU252UlVDUlFMZmdrblM1bVV5ZHVJamZEVmR2R2x0WDRoNXhCTm1vQnZBNVJ3b1NxemVUOVN5M0ZrV0N5NHNoS1UxeWFRaDFOMVpfYTQyUWEwbWRLM1JiTWJVbEdxa0ZacTJwV1lLSEdYWTNicjdlcURibTFaeVc4WU9xQ3k3OUFGdk0?oc=5</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Gobierno Petro destinó $88.840 millones a diálogos con grupos armados: denuncian alto...</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3700,6 +3700,63 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-12 14:39</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Iván Cepeda defendió la Paz Total y aseguró que “nunca” se arrepentirá de participar en diálogos con grupos armados - Infobae</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOZjdQUGV6dU8wTEVUX2tWWW45Y2RybFhVMDhCMmllQnF4MHJUTXAtMm1RX1BELURrc0dMaFhzWDNQVUtTWkhuMWxWS2JlVjNBRWVRTENYUmtIUHZyUDNiLVBic2ZNaGc2STJXWlBxVDdLLWxkVWswVG9Nay1Sc3VNR3dQd1BiTnFZMlVpTF84SUY5QjVDWG9rVW13a01yTjZiQ0Z5MWdVa3FvQmxNOTQ3aHZDN0h4b3lWNzlNQllocUI3VVl1U2NPckgzbUVmOXdmbnFQTnpmWDk1TUFrRVNmd1R1b0VoelI5bW43NUJKd9IBigJBVV95cUxOVjF3U1gwVXU2bnRlR3BQQkk0NFBvME9pcmxhaXZta3ZqNmFkdmVPa1dxVXJoSnVLUHFrcVhQQkx1Szh2NnZDeEFpYmRWS0REeVhaNXpKSjREQndkREFhWHBNaXRyaWdLb1NOMVBKOEI0LVZENVM0SEJXUjlIdXFEMk9rNHo1VGVmdklWQ0NGSnJSQXp6emp1eWtoS3FVbkVnVlZKQnJFUEh6TzZrNXpVQm1IeUxIT0ZuejZ5UV9VQ2swVGRiOUM5Mml4UnQtU3lBX2hEc21PUXZxellqYkJEUmpxd2I1VzhYekVfSFJ5NndiblFaR1E3aEhnNWRSelZMSzBnWXZXTGNrUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Iván Cepeda defendió la Paz Total y aseguró que “nunca” se arrepentirá...</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3757,6 +3757,177 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:00</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Denuncian gasto de más de $88.000 millones en mesas de diálogo de la ‘Paz Total’ de Petro | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPM0E4Tm50d3R3b1ZaRHNnRUZ6LVpaOFhqMUZoc1FYNmFuVHdNczhZV1VHSU5TNWhleEJCNU8yTGI5Vy1admROcXhOVW8ydU5uOWVKQjJodDNseVdVRE9PVUpPQU9LRUh2X0V3djdDYTJOeDg0dW5DMDdvamhlZnprcjBRQWh1bmU3d2pxQTVhZXFRVzVnQWhPQzB2Vlo5Z1VB0gGmAUFVX3lxTFBsMTBhTGlKUXFnN1U4TmdoNEtKOEtiTmc2MzNMWmNIeFBMRnc4ZmNtVlh4Z0gyVGN4cjFlLWl0U2JDRTBJVVkzamNBZFBvLTlldzJTX01DdjlhTEFoX0ZrVHJYMXVfdFRCN1hGYkd6NV95YzlqUTA2QzBfbUFJRjdqR3lGVlhqMXNjX25aSGdKTTUtRmd1RnFuZ1JOc0hxMG02SnhkV2c?oc=5</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Denuncian gasto de más de $88.000 millones en mesas de diálogo de...</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Departamento de Estado de EE. UU. cuestiona decisión de Petro frente al Clan del Golfo: "La Paz Total no ha producido las mejoras previstas" - NTN24</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxOdk8xY0w5bEVQdW56aDRxcUtuZmtEdkJ4ckM3aC1lVFM2am03UkgzT2RNQTZrbGFGaUNpVmhyNmFESkxIT2p3d2R1ZGxOMV9qMXl2WDVnMFJ2SVNNV2U4OXNyMzRybk5PRzZ6VHkyOWxQZ3p5eUljQ2xrRTlNcjZvSUlRanowU0lLbHJyM1hWTHJhWm1VVWdpOGpGWjNkYm1BRmUteTFwdlE4cmhoQllZRy1NS0RoOGlTWVZIdVZQZ2M1WU1ZWHltVU5UZTFpRkdGZUJ6cmgyNVVLaTBiUlBQQk5RXzVqZ3RhckZTclJRaG9USEVNV1pkaDZzeE5CbGFhTkVwVkNycDRhTlEwUEViT1lB0gGSAkFVX3lxTE1udjh0RWhQNFQtREZmbGl5VU9HQmo1TnJSQkxCcW9yYTNFV3g3VTZGenhFdk9ET2QyMGhTOHp1dmVxLXRVZk5PMElVcG1VN09ZOUNOc1AwOGxjWVhBMENmaHRGOHlVLUVmT0VYWDEteXFOZEZTOWo0dUJZbmc0M0g5SDhBS2lyY1pscXdTZGlqREk3cktTRG0yMm5pazhzaGNPT21FZU9iUGhCZHd2UExBekFOdld6SjYyOHBzaUpzVEU3QWs1dzQ5Wko5YUF5aEVjODhiLTJsX2ZTZ3VzN0lzdEFtSnUwbTR0STlIQkJkbFpTTkxnRkhjZ2hVczBQSTdnRXk4RUQyYU9rbTRYSFl6RlE?oc=5</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Departamento de Estado de EE. UU. cuestiona decisión de Petro frente al...</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-13 00:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Revelan millonario gasto de la ‘Paz Total’: más de $88 mil millones en mesas con grupos armados - Seguimiento.co</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOeVhtaFNYOWhndllhelQ4NGlsY1FfSHYwcjd6eTl4eVNwQUNZbXI3ZmhqUmJheF9FbUVtS1VxOFhGUEdjTjVEMlFMcjBTejJ4OWJtOWNybUtiZWY5OEl0MG5MdGYtYWJpVVNDMmI5YkhuTEdUenpjRXo1N1lDQklnX2hTUUVYM2VrY1B1dXJ1LUdzbGhObkVRelVZZnUxb2NUS2l6akxOdHdYU0lCcHZ6TTJGQ2RyZFlTV09tRWdvemY?oc=5</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Revelan millonario gasto de la ‘Paz Total’: más de $88 mil millones...</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3928,6 +3928,63 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:47</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Paz Total: ¿Qué candidatos a la presidencia seguirán con la negociación y quiénes no? - Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPMnFQa0JTeTRyR3dKNVlwVFJTWUtlQXF6ZnZNdDhwSXhERlJkVkJ2MzJjZVpTVTNpTTZDXzZwZ2YxdW9ubkE5SkZOX3BBTjhUSTBmSFczcC1TcUVsYnJweW9mS1Rva1A1T3UzeDl0T1BORTg4Uk5kOUpFdEV2a1hpc1ZkaHlQU2ZmdkIyOXFJdVdNSDd6NEdoTVN1NkJxeTNnWk1aeFY4T3AxQnY2S0NtQmdzUHRxa3F60gHMAUFVX3lxTFBTZ21LYmJRQ09FOEM3S0JkX0hxZ3Z2Z1UxaDJta2hobUpFR0NfcHVrbjdkNGtSLWZqT3hTNW1vS0NlRmlKQjNDdlBlemFIUFVjRndUa0JINUNtMXl4bE4zRmg2ZlVENzd4MzNzWW5XUWl0ZENTbkh5REIybkVOZVloRUhKeXR6dGF5TGpXTjNEbG9jN29WcWh1TmVwTUUzSUVrTDhSeWphcXhzVzRPdFhCUkJMZXlnMTdXSjZJRHNneDBxMHQtTDdLMlRJcg?oc=5</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Negociación</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Paz Total: ¿Qué candidatos a la presidencia seguirán con la negociación y...</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3985,6 +3985,63 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:48</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>“A la gente no la mata la paz”: Iván Cepeda habló de los diálogos con el ELN y 'La paz total' - Noticias RCN</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPbXhtejQ3NDVnLVBXazlOV3BxeVZiU0xFa2RpNnVfUmpzems1S19RYUI1TTVFX0ZQWG5pUVU3aG04XzJjc2NocjRENE9zNFBOdW5xRl9iRVpVRmN3Q1l0Ykp4SmpmeGdldUE0dVN4bmNWS3FlNkhodGtteFV2anZ3dUVLdm5MeEpUZW01ekpBYVNCYTNUZXVnV1JMOUt3UWdNNFVqaWZfMXNkaEJOZkRjTHlZRkRKN1dYdE5QT2VwaXA0blA0SGVHcmcyc1o2QdIBzgFBVV95cUxQRkZySE94RTBiUVpHNm1hakhrTHFueW5fY1JHQUZwOU9mNUlzYzBaOEczQUJzdTlyOWgya2wyb0tzazJRSzBkTVpBOUlOVzl3ZnJiZ2s2T0ROTHRMWk5WSzIyR1pjMDZ5OUE4ZGUyaVVvR09Kenc1U3J3am5TRnVkbWRYcW9sbDVVNm1WNEFPU1Vtak9NMzNJNGpGS1JrdEtmT1U3X2NtNTd2S3NET3prdl9YWG5OUlBpRVVzWXp6LTJDekVtQXpXX0U5UUtpZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>“A la gente no la mata la paz”: Iván Cepeda habló de...</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4042,6 +4042,63 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:40</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Petro juega su última carta de la paz total con el Clan del Golfo - EL PAÍS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNWF9sQkJLOE9FU2JqSlpINHVmRTNIX2pWYmltTDJBZEJiX0MxWExUZWxvX0tSVW1KaUQwb2loUDJTSndoVWxqVkYxUENMZl8xMnAxRHY3YmNqQVd2Zk8wc0dYRjl0alp6SjNmMUpfODJIMS16T2hrUGV3YTB1RElsenVPRXdFSnN4MGhkU1otU0UwNXJDWWJHT0ZHS3JBekRCVXQxMUNGRDhXMU05R21fTkV3Z21wVm13RkU0anVuZl83alRyY3RCUHRzSUt3c2k1TU1Zek5uUTBhRm_SAe8BQVVfeXFMUF8xb1JNcXBhWHBBQmtYdmx2eG1pWW1rSHhSSFZzUDBfczFvbEpMekFiUDJPaWN2Q1RTYXBFVGo3MnVYZ1hMMXFoRHc4VThlM3Zsa1N1QXdGenJQLWR3NjNuRWNEYWgtLWxLbnYzOVcyTzVnbzZQbmRSc2JZb0RwX3RZMmZYQk5iZDc1ZWdHeUNaYlhvbzJrMEp3WXpiQ1AxeHJQMU5VcFBUUjdBWXY4dDVIZG1LNk90ZElnS2VWUWhtUGlOQllBRkk2VmVSemt3YThVSmZ6S29Ra1BZVVNucXItaHp0Wm9ZMDlWaTJxUGM?oc=5</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Petro juega su última carta de la paz total con el Clan...</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4099,6 +4099,63 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-29 15:58</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Gobernador de Antioquia rechaza la reanudación de los diálogos de Paz Total con bandas del Valle de Aburrá | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQa1BqQ1RlSzZYUU4yZ1BhMmd5cHZ3eGtDZi1hck03bjRLa1pGXy1FVWJ0dmxsZmxRcGt0UUFyYW1DOUJib2duZFZiRDI3QzdFSDgwQUdvemhSbjdHTjBKRkZDRURmSEFreS1Xa0pkWlpVaXgtTTlwLTBYOFpral9WdnN1Y2hncEJNT29RaUdNbzFSdEVhbTNfVm1yaDh4N296Yzd1a000MzJGX0YyQ0xBT0k5Qm1fOVFSLVFIN3lDbGIwQdIBxwFBVV95cUxObFNZdl9UZVM4VUR2ME5USHppZktaLTV0MG1KOUN3bkJPUFJfQ3lRRC1yNFJHOXJ0T3RVRHZ4QTlyYmR3bld1djRjbjFxRXlnajdlTW9QN01oSkE1Z2hVTm1xNWluM0R6eU82cmJWZTQ4SjhRaEU5ZmlIY3pSWkp3djJMUnoxbzdnam1NQ3F4TGNmTThNbUZLT1o4SE84cHUxRHJfUUtCT3pfbkE0X0ptdy1sbW1VNmd5T3lXeFRuSHVRdEpNYkJr?oc=5</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Gobernador de Antioquia rechaza la reanudación de los diálogos de Paz Total...</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4156,6 +4156,63 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:53</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Promesas y vacíos en los planes de seguridad de Iván Cepeda y Abelardo De la Espriella - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNZHRCVlR1QzBNRjl1SDd3QXY3eE1rTFgzX3pENFdNRmw2QVVFOHhTc0RDYWRVOWlpOGkwYlB2NEdWT2NiQmkwYmQ3Z3lNaENBbjYtRnNfbVN3Y2xva3BteW0yU3A4M3RCd1hJRlRWRVdXU1VveFEtUEJVaTBBSF9yYmdCYkF3YUpabDlrSTFqbEdoTDQyS3Q2R3dWTnA0ZEZkNWZCeGxaTVdza3JtMndGQ0hOaWthWFF2WTNSQ3FJRW83NnphMkF6bXViTm9CaGxx?oc=5</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Promesas y vacíos en los planes de seguridad de Iván Cepeda y...</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4213,6 +4213,63 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:17</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Gobierno suspende operaciones militares en Putumayo para facilitar concentración de disidencias de la Paz Total - Infobae</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNUHpReG51VXlVSWdZQ0dEQzExQzR3WExGWmRkc1RpZWlMZ0dhWF9qb2puSXZNY1FBN2cwUUhsT1RxTlNiU09tUkNELW9tTWpVOUVMZ21rb3J3THM2RUJadHVLdFBZSG9WcVdpbElpWHMtRGVCWjJyUTdaMlNURDlycGtSdWRUUHIxRFpLUWxCd1l3X3duV3EtMHBUWHhaVjJhblN6aFRrRjlpSWdDM0FSMVM1ZFVyZldHaFhpUGVvODAyb1BhQWk5OXZXT3JjMlVabDhkdHZ5aXdoQUtDSVk1Y2lYZ3d6TGl2OVBOWdIBhwJBVV95cUxQZVNpczU0MDlILVJLei1fcFoyS3lNVGV6T2NHcVQybjBwczA1a1U0dDcyYURtelNVQ2tXZk1GMjNnVGRUOEtqZ2s0ZDFMZkJhTlBwdnUzNm5FTmpIV0p5T1NiU2F2RkY0eUJjeXg4VFJUQ09FOXhtWmhuUkE2cm5UVHZYMzh2LTZnaVktLWJ5ZmVNbFJDR1hmaFNkbWZncDdZbmF4blZNNldzeld3RFY0aFpVTGtpV1k5MURKMG03eDhSVjBfdlQ4bmhmeDdoYlg0LWdXRk5aeHdPLXI1VFdzNFdyc0JPOGJOOVA5Tnd0cDlqXzJVXzc3NkNmUkwtdUdvMVRycDVqUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>EMC / Disidencias</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Disidencias</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Gobierno suspende operaciones militares en Putumayo para facilitar concentración de disidencias de...</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4270,6 +4270,63 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:09</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Enfrentar al ELN tras el fracaso de la paz total - Defensores de la Patria</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOR01EamJUN3JnUjRFSVJBSWdLQVE4eXZMelptUTZNbndSdjJqVE42NlZWR1AwdVhPOGVCaHl5NDZsajZJaXp4TGdMWHRuN1NwSnBDRF9fWnl4SGNIN1NRUWdvNkVLcFZNQ1lIbnMzYmpmNDd5S3M4aFV6Q2NZemlGVVlPQjJNZThhRmpKNDBBdUVuSFRxWGVJSlJvS3IzVWo4NmNoMVY1eHJYcE1zY0hUTXR2eE1rWWdmZjdqQkxaMHQ2cHI3N1pR?oc=5</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Enfrentar al ELN tras el fracaso de la paz total - Defensores...</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4327,6 +4327,63 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-24 14:45</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Audios sobre acercamientos con el Clan del Golfo generan nuevos cuestionamientos sobre la paz total - Meridiano70</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1RbC03cVdpWmIzMmxMVmVHeW5rRDFPQ3pYcm8tYlVNM29KMzBMUlNfRlVJZG8wUmRHeDJSQ0RiTTAySFF6dHlZZ1lNbXppd3U1R1NsYUhGWDdBczhsMTBqRnFuaXJ1RlltWWdVNWhobG9yQ05u?oc=5</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Audios sobre acercamientos con el Clan del Golfo generan nuevos cuestionamientos sobre...</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4384,6 +4384,120 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:14</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Paz total: Gobierno habría ofrecido suspender bombardeos e inteligencia al Clan del Golfo - El Espectador</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZTRra2V1SmdzN3luQ2RnSzJXVDdQaWxsQWZZb3Z0UmJCN0c2Vy15TEFNdkt3Y0lnTUxlRGZBMzZpcEt3RlJ6MG42MnAzQ3JiVEFma2U0ejQzQm12LTUwRjJRejBLbDk1UkJuTzNrbzEtOWQyUEtWXzJNUjhsVks2ZHVqdTY3VFlFNVFpYThCODVTS2RHY2ROeFlkRlRLWlROZ1c1d0RYN2tuS25JdXFneXdJb3lQNFZ3cDkwWTZtU3kwb1JJal84aG5PQnYzLUhhczRrMkpCOC1xMGRQTWk3Yl9iUEZZdXd3b3BWOTR1ZDVlcHdkN0xzR2F2dXBHMV9TMFHSAZYCQVVfeXFMTjdHN3A4N3FTVjNla25acDlqb1lQNUZrUWtpREZJb254ck90QThTeTdvTGl4bEo1dU5qQnJER3RQcl84ZXZIVWNKaWVyTzMxa1EyTHNTTi1wanVqTU9QZ3VNMGZ6MmUzZEV4a2x2OWcyelpmejJucS1meVZVUG9jZGo1bHAySDY3WlFGakw5TmhDRFZiM3d3UEN5VUxZRlU5RjFZUU9HR2F6WW1fZ09UcEs4WC1NQjRCYzRNTnFIeUNiYnlheURYbUNfTndrc2s4ZlBxUDN1MDZZVlVtMHZURTJQbHktVnBhQWFhN0NyTmY1NFFQQzAxMWFsMjdzUzh6MjR1VUsyZ0FCbk9zdURiTHQzWjEzLXc?oc=5</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Paz total: Gobierno habría ofrecido suspender bombardeos e inteligencia al Clan del...</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06-25 00:14</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Revelaciones sobre presuntos acuerdos con el Clan del Golfo desatan ola de críticas contra el Gobierno Petro: “Es un traidor” - Infobae</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxNRnQ1b0pIbTFEYnl2ekZvcE9pZUt0YmxGMHU4SWVvd2JFd0NlVm9kQXpySS1feW96QzVSNnk1bTZXZVctMDZXcDBnRXNtMlF2RVVwM0pMSjBLLUFsR19yOTRyRlVPMi1OajVCQXQ1dzc2R01mbzl6cmJWWFBQT2R5RDBDTlVRRDJ0b3liSWIxN2JJa3kwOHcxMll0MDAzY3FxdmVoelFuazZGeTdVcnp3MlZpSWFZdFBNd0g5aC1wZHVTT01VRWRWbGd4ZG9hOTFwQWZRcExaVGFEX215cGMtN0pSZE8yZ3N5cWpGU1NNMHR1U3AwWHRxWkphVdIBlgJBVV95cUxOQWUxYzdaS19iNndjSm9WV3lUNU9QYkxoT25OOTJwNGdOeXRZcS1CTlVuRjZnaWw1Zmt4MWNfdUJMbEpFSmJJWjhWdi1qanhmSnZKZ3F1alM0ZTQ2T3JQTVo3bFRjWW96dXh2NFhxLXJIUGxqV0dPajVrOE56QnVMNWx3Q0ZwQWVURUpIdGQtTVVneElkdnhfLTBjSGFvbmZiREJ6MXZQcHdwMFc2X0RHcnJiVmhaQkc0dTBFZmVVRE85bHUzclR5TnZtZDRHc3ZZekIxVndVek55MFJLYUVLZTJ0cEk5MzlIU3BqOTdvWDJSNHZZaHYwX3BybWhlQXhFY1RHUVQ1V2hkU3pOX0o1dlJaTXpHUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Acuerdos</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Revelaciones sobre presuntos acuerdos con el Clan del Golfo desatan ola de...</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4498,6 +4498,63 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:46</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Clan del Golfo creció un 100% en el gobierno de Gustavo Petro, ¿aprovechó la “paz total”? | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZEMwS0tjRkZSMzdUaHpVTlJ5elpOZ3EyaWJPVGtpWHZMbFpiZ1JSQ1d0WWpHSVZST3p6c3VOLVEyZnNKNFZPR1FjMjFvLTZ2OERyQkNCOXlhRHZ6OS02MU5kQVNYQTQ5SllMWW5RWmprNEQzMEJ4RG9tZDk4ajJjMnNYVXd0N0c2MEUzTGtfSTRjUnZzLVZicGVIcVR5WGVIdjdMVGJrRnFBa3J6UXctdjdwRVA4T2VVMVHSAb8BQVVfeXFMTmd5M1hod2VGYjFFUVVYYTk0R1E3LXlsNHRPOVpZWDJNbG43U0RiMWRMNFoyWklTeldpT1luSEljeEIyLUNQaGgxN3FQSDg2eURnejh0bDNmd2RtNXdQOTBmVndHMTFiTHlheEZIR2lLVlRyMV9EVTlRbTBVanJVVW4xU1JMQ2xZU1BvcktRdGdmY3JVRFZJa0s3X05XMTVScTZHMEtUdnVtMUxOZGRHeXhUNHh1NEtpeWZvZ0dhTEE?oc=5</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Clan del Golfo creció un 100% en el gobierno de Gustavo Petro,...</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4555,6 +4555,120 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:10</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>El caso del Clan del Golfo deja una lección incómoda para la Paz Total - Fundación Ideas para la Paz · FIP</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOeFF1OUVwaWU1ZEJ2TVdncXJ6a2piOHp1eEEzQWJBeVFsR2hkMmV3MFdyeF9GcFVVTDVXOHpsTnBERkFUMEwtQ0p3RDh5UGZ1Z3JzbGNJN29MZmZXbTY4enhvZlRTOFF5ZThhaHcxR0FWcW1JYTBNSGg4eXQ3Ti1jeXlYQ016cEpFeXV1QXFjS2YyNTY2cFdSalNDOThHLTRwYTZyZERjV196VkNrREplX3Z5NW1wNkprWFVmM25kOA?oc=5</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>El caso del Clan del Golfo deja una lección incómoda para la...</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:10</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>El error que, según los expertos, hizo crecer al Clan del Golfo durante la Paz Total - Minuto60</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNWmFLak5wU2NjSzlmaVZkVVl5THA1STZoY1JCRUJuNUdnV2xBQ19mQllaZTV4QU0zWk5YUGx0ZTlDdk5KaEMyTmhoNWRVZWtpQkl4LWdOdlR2Y2tHMWYxWUw5QURpYWstQS1JUGFnVjdIbXMtNGdLUnVVMll5S0lXWmYtWGtvbnhEMzNKcHFR?oc=5</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>El error que, según los expertos, hizo crecer al Clan del Golfo...</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4669,6 +4669,63 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-06-29 00:10</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>“Juguemos a los congelados”: Pacto entre la Paz Total y AGC - El Frente</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOSEhmV3UwYUpuTjVJRE5IZUluWEhtbFZmbmJGbVlkNU5zN3BYNHBJTmFDcHRhUVVLVEN6c2JJV1BGdk9oczMxN1VFeHdOUUxHOWtQZzRWTzRGT0Y1U0hYdllTb1FoX1k0M2FqaVN3RURBUmtRai1CdkVJVmxsOUhNR2psYzdoMS1C?oc=5</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>“Juguemos a los congelados”: Pacto entre la Paz Total y AGC -...</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4726,6 +4726,63 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:05</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Rodrigo Lara criticó la Paz Total de Petro tras escándalo por ‘pacto secreto’ con el Clan del Golfo para frenar bombardeos: “Artimaña del Gobierno” - Infobae</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxOS19CUUNiOXFLTWdEZUt0UFFnN3QzMlFsRWQ3QVBxZVh6VG5UNldidFlOMzNPalRIMkg0OXJ5LTdyWFdKb3BLbHY2bERKc1VoY0Nya3M5cnV3MzVGQ3NCd3RaSWo5Mks3QXlzaWNBYWlXN1Vkbnd5cWI1cDFrV2lPWTFGNjZBWS1fZzdPLWNaVU9XUGNTSkozd0tMc29LZ0k3ZWp2d290MW5TWmdpN1hQcE5vT1g5QlJpQ0laVFNjYzFJb0hXUDJXbWt0TXZvMExRMi1JZURhLTVVS196cjYwb0pCZ1VPSzZGdkJtMlpTY1BpcXprMjEwbFpLenl2VWtFT2Y0TmZsdjBWZGN0SWVZb0JtV0pwZ9IBsAJBVV95cUxPTExwLV9PSkE2cEhlZWdhZW14eTdaN1Rsa3JLLTZXYTNYbXFWdlBOdmxiNFlhTkxXMHFiaE55b0FLY045X01wZ0VDMnczYmNienZDVVNCdzVrWU40TFdONWo5ZWxINUtUbG9ndDI3d1NERkNJMUVwVW8wMDZBN21XRzhUd3lqWm1YcURYcDROT0UwSjFqZEQxRnRYNWhVNGNjOGIyZDdzRFdGV3lfczR5YTAtRU93bUg4UTN0Wi1iMHgxeGlYZ0c5Z0s5RWVqWWJPWTNwdzJyekNXS2lFS2JWVjQzWGJ4enFUYkRXVFA5QVNNZXplRGdJdTFVYzBmT25mLXVhM3p1NGZ6MXE3WFlmenlVSXI5Q3pEVjM5TUVxWDhUU2dmUHFLYlRpZUcyNDk3?oc=5</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Rodrigo Lara criticó la Paz Total de Petro tras escándalo por ‘pacto...</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4783,6 +4783,63 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-02 00:08</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Consejo de Estado sugiere que Petro no podía negociar la 'Paz Total' con la Segunda Marquetalia - CAMBIO Colombia</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPNXFhZVJlVGc4c1Vmc1VYQ1BwRHg2NDdZVUJDTlJJNl9OSVR6UjZXMUYtTjVRbHVjbHBmb3kzN0ZVM1VmVms3M2xZODA3V1NuWkJhd25qanZMQ0xxQ3Fpa2xreXlab1NoaWlVQVd2NTl0U1BvVkVBSk40Njh0VmY0cjg0eXRFT2JMeU9PeWc5VFlRRnl5WUdsQVBISmhNcDZTU0dTbF9NU1JhaEtxSnNSMGppaGhLc3M1S1U5cTV3RmtyTzNZMlUwaWRDT1hUdm9SZU1rRjBKbjFuQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Segunda Marquetalia</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Consejo de Estado sugiere que Petro no podía negociar la 'Paz Total'...</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4840,6 +4840,120 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-07 14:51</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Criticar la paz total le costó el puesto al ministro de Justicia: ¿qué dijo Cuervo sobre las disidencias de las Farc? - CAMBIO Colombia</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxQM3hZQlBHb192QVpRamIxSEVoeXpMNXB6Z3QtMnZTRk52NHBCOGl6YUNWSHZXTmt1ZDRtemlLN0dsY3lWOGN3QzNqN2FxUWVUdlNZSjdyc2IweS1PU18xQk1pdGhVYWhZMmNRNThQcnlqYlhualNmTmltWjN6Uy1sVFd0UnRWYnl1ZVkzSENoalUtUl9Ud2E2MHpRSkdjUk82bzVKS1ZVd3lxM041NHhULU50WDZJUVMxTWZOS1d4Y19rdFpUdkd2SG9QR2xmQ2dSSlNtV2FFbGx0dk4zRjNRMk53TW9CSVg4SEJLd1ZlaE1TQzA4YXc?oc=5</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>EMC / Disidencias</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Disidencias</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Criticar la paz total le costó el puesto al ministro de Justicia:...</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-07 14:51</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Abogado del Clan del Golfo se refirió al polémico audio sobre el supuesto acuerdo con el Gobierno Petro: “Si es real lo que prometieron, lo incumplieron” - Infobae</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQNEN6M0RjSmJzQnJUUnpFUXpfRWVFRXh0VzRwelFjVTV5dHVWRTg2ODRQRVpNZlJYdUFzM294MHVqMnhGYl8xa3c3RTQtcUFqVGplUlpWRkhJX2otQmZEejlnRDVhb19aWHVfNFlrWjI0aGJRc01aQ2UzT0hNWG9jOWU3ZTNHQk56YTRaQnJHUnllOEdBelp0blpVYi0tVGhSNHRzNDJ0MENMNzF0aExpektxTFdoeEFsclNUNXk4T0lzc3RsWjd5b2NpcGU2anJSb2xpTDFUdDRpT0hjUzdpTnFwUUI1RXoyb2Z5SkM1Uk1zN3QtS3Qzb0xvcURBUGZlaVl5SlVNbnNKUdIBpAJBVV95cUxPMWN4Zm1JdWtBRnV0VGtLM1lTbXU1aG42ci1lbzRIZGFxSzNvaWJPUzZCb2xGbUdQY2lXdXpqdzhOazlTdVFiR3kwWUNZWlA0dnZRdEhCS0ZXLWZrYTI2c0dHOTJKSllTV3NBMVJrc05zSlBMZ2pZWDFRaFFLUjg5eS0xYlVFLVNDbDh4TTVMMU5jeWtrQ0RoS21tcEZYQTRxS0JObERMbGwyWWpRVFJaZ3lqV1dYSjBRYUNqOWlkYVdTYkhzS3FXTXlrVGpHRUwxbm1samgxRlltMUNiTEtQYlhTd3FDODdyZ3J3RlduUUxXTDZjN3JTMTVQTFdUWVhvSWhvWVdkbDFnT3NFdnRYTENLWjMzZFZUVThPZ29WUVpkSjhN?oc=5</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Acuerdos</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Abogado del Clan del Golfo se refirió al polémico audio sobre el...</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4954,6 +4954,120 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-08 14:29</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Las promesas del presidente electo de Colombia, Abelardo de la Espriella, recortan la farsa de la Paz Total de Petro mientras la violencia expone el fraude - LatinAmerican Post</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxNLWl3cEd1bU15RG5helI3ZVhJaXA5cE9hMkxZVVpxYjZFeTZfUHJRWjVFUXY5VEIycFpaSURGbmlleWNFMGFxVFZjaGhTaGZRcWJIMHloZ05wTmtnUkdTck9jTGVXQkJ5QjRDXzRWSDhoWUwycXVvbEFCMkdMNlducnJLQmRsNEhXcWpxOHF0M3NFOGxfYU9INDFVUTdBQkRyVzZvdGZOU3cxaVR1b25rTDJaMXZPVF9USm05cnRVZjhNUXdlUmhSOUtCc1VXclhITG9JbjdveEdwNDliQ1c4bHVQZXhVdmc5ckRjY1I0dHg5SGpaYXpicV9na3FSRHVlYzR2TjVYNWpMYkphLUx5QTFyQjJ0R3BPbkE1WW9fTGZDYzJzSmc?oc=5</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Las promesas del presidente electo de Colombia, Abelardo de la Espriella, recortan...</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-08 14:29</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Otro lunar de la paz total: los impactos de dar estatus político a las disidencias de Farc - El Espectador</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOZjU1UU45bk44LXlCSk00NEJ1SklscVJlT0hvWEhRM1dtdFlpdkR1LUVac3E1eDV1QTBmby1fMS01QXhVd0hRaTVlOHo4cTU3OXZvNFFZcDhrQW83NGNGbENsa3hkYWpCb0FVNUdwZllVbGVlNzRmR01TREM0cF95MzJPYlFZUHVtcl93WWkxTkJLSFAzdFE5QnhqWFJJTjlOSjZpVDlwR0xDc2NQc0FzMXNlRWl5d0FJeWtHNjhUREljT1dWM2Vn0gHbAUFVX3lxTE82aDF0ZFVGTmQ1M1gweXlOSHhoa05QSUNkWG12ckRxMkQ3VzZybmhORllKM0hzVXRUekFyUWhLUTNPaGozMmtNcXNVRFY2Ylc3UE1nbzZPZ0NPN1ZYWDUwQkEwdFRQUjBiMjE3cEU5eFRzNHNydmdlTTJkRlI1WEtaYTVMZjBzc3FFbFRzclJzNDNGb3ZnWWwtQm9UMlprS1ppeWYzMjFncm9sWUs1VVM4OWJ5UFByYVFOQ0QtRnlkMEE5WjgwcjhEOVNPVVZubXlCbENqYzlLWnA4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>EMC / Disidencias</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Disidencias</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Otro lunar de la paz total: los impactos de dar estatus político...</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5068,6 +5068,63 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-09 00:11</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ocho miembros del Clan del Golfo desertaron en plena crisis de la “paz total” con ese grupo | El Colombiano - El Colombiano</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNREUtUXd6SXpyYi1Bc2s2TTJOeHExNkc3bUdBZC1IWGh0czNmR244M0J5S0t4UTNoZWFsNllHc3hUeFB0TTRTWHBYdWdMcUlQMEVmYnprN0RkdUpBOTFCYXAycmdPMGlmYmUwUzJEMTN1UDhMVXJ0cnRUbzZxbU9ySmx5Q3ZlV2pfWmpzMWZjT2NtMWpOQ1hzZFpUWW02VmpEbkZvRnVBbnJzWWtXQ3hDQ1EtYmpzRTMzWGNiYdIBwgFBVV95cUxOSjdEbnZKbnVWTTlLS3RYVXRXMFIwQkdGQ3hISl9Pd1dEZkEtMVZGaEFzNkFzTlZZNS14ekxWSnBiNmpObXFQTzBtbUxlbHhHcDJ1NTFzcjVQd3R6TnAtSHJ4QjF6MW12NTlMVnl2cHp2N19YV2JfRXdqdmx5X2tsam43X3ZsMjZvQUhTajZVSmtpa05RYlpRQ1U5OTdrTXh0c2dCeV9HYXlyd0JWaTltX1VqSHdxc000TS1yR3RpU2lTUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Ocho miembros del Clan del Golfo desertaron en plena crisis de la...</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5125,6 +5125,63 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-24 00:00</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>"Mañanas BLU con Néstor Morales" Plan del ELN desde Venezuela para asesinar al fiscal: la paz total no puede ser a cualquier precio (Podcast Episode 2023) - Metacritic reviews - IMDb</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTFBzTXhnSmhHTnJNU1ZLVk53Ymp5MHdCQXVVaTJCaWV2a2JVX1FHNW9oeGZFOGZZNjUtSFlmTkpIM1VlWV9lNGxYQloyLWpPU3FyTWx0elJ4X1djVXdLQXluREFn?oc=5</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>ELN</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>"Mañanas BLU con Néstor Morales" Plan del ELN desde Venezuela para asesinar...</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5182,6 +5182,63 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-02 13:41</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>El legado de la Paz Total: más mesas de diálogo, más actores armados y una guerra fragmentada - ELHERALDO.CO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPNVBFWXZKSXc1S1p6QjBjaWVYLXZvYlVhSDhQM2JxcFRsdWJVYXVnVXJlb210UUt6LXZpdnJNcEJhVmQtU0hyN2lqeHU1dVN4N0RoTDZPYnlhdWhlc1ZPMFhWQlJnNEJNeG5NTG1yVjNqN1g0S0NNU1FOSFhmN0gyd2txRldpNHdPMktvaWUyREo3R3lwVUFxeGhHT3hvd2ljaDFxVmxqY2Q2Y1dtamlOcEhkVHFQVjdnV2VKa0ZFRlRBa3gyZHR1eUg0ZzdEOXFUQ19r0gHuAUFVX3lxTFBETzJuc1ZmZDktTVNNNENuUTJxWnFMTUt1S25QZWVfU2pjS1J1YXdEN2ZsbmFDTHJLd2JiRjExNWhyWkxubGRNLTR0dVlDUC1FN082bEwxQ3VMdkNOV0dtY3NTN01ycDd3clRPNkNfSUo4VHFXZUY0Nm9wd1lyYnoyMkswNC03dG9xQmdlWlhzX1E5OUhaUlhZUnRHaTV1bkZ6b1NnODRMeFZyU2VfakJqbmw4clhhT2ZHVjVzTG41Mlh6ZHZVNEpYZldnOHpVbkxuemZnV0twa09ybVVtU1JYdzFPSmItWGVWcXV6Vmc?oc=5</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Multilateral</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>El legado de la Paz Total: más mesas de diálogo, más actores...</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5239,6 +5239,63 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-05 23:59</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Noticias</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Pésima negociación: grupos criminales crecieron un 90% en el marco de la “paz total” y suman 28.802 integrantes | El Colombiano - elcolombiano.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQdTBNaW9lYmJSZGdjamJWamNUbHdJWnFSdnpLdGNaTEpaeUdnSFZVWl9QZGJvVV9iOUY2U3J1a2lqc1M4LWZvb3RTR0dkYUQ1N0lrT1Y0ZURoNmhqRXBzZEs0c0lkZXVkN3o5UURwdHFBN1N0Q1hIbkFKSHZKLVpFUnpfUjk4MUF4Y3NoNDVvOVdYNkZVekh0elhQWHfSAaIBQVVfeXFMUEZoMXE5Zm9PNDk3Z0F2NEpkMHRKc3dMVFcyZjJMalh6LXc1ZUpJUXVqNnlxN3BRT09BS1dwRlp4UHZNOFF5d2h4Mk9UczdHTWR2S0lPTTA4U0xIT3BmWGxVblBNbkd3SmppeERpOFBrTDRQeW1KNUpyOVV4OXRxekM3Y1k3WEFwZHJiZkdKSWE1N3F4V0JnX1NjMG8xXzBpV3N3?oc=5</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Negociación</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Pésima negociación: grupos criminales crecieron un 90% en el marco de la...</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_paz_total.xlsx
+++ b/historial_paz_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5296,6 +5296,63 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:19</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Podcast</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Paz total: Gobierno habría ofrecido suspender bombardeos e inteligencia al Clan del Golfo - El Espectador</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxNZTRra2V1SmdzN3luQ2RnSzJXVDdQaWxsQWZZb3Z0UmJCN0c2Vy15TEFNdkt3Y0lnTUxlRGZBMzZpcEt3RlJ6MG42MnAzQ3JiVEFma2U0ejQzQm12LTUwRjJRejBLbDk1UkJuTzNrbzEtOWQyUEtWXzJNUjhsVks2ZHVqdTY3VFlFNVFpYThCODVTS2RHY2ROeFlkRlRLWlROZ1c1d0RYN2tuS25JdXFneXdJb3lQNFZ3cDkwWTZtU3kwb1JJal84aG5PQnYzLUhhczRrMkpCOC1xMGRQTWk3Yl9iUEZZdXd3b3BWOTR1ZDVlcHdkN0xzR2F2dXBHMV9TMFE?oc=5</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AGC</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>No claro</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Gobierno</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Paz total: Gobierno habría ofrecido suspender bombardeos e inteligencia al Clan del...</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Noticia</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
